--- a/src/attributions/attributions_saliency_traj_454.xlsx
+++ b/src/attributions/attributions_saliency_traj_454.xlsx
@@ -2137,2278 +2137,2278 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0008201407035812736</v>
+        <v>0.002137402538210154</v>
       </c>
       <c r="B4" t="n">
-        <v>0.003541743382811546</v>
+        <v>0.001291204593144357</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0003965444921050221</v>
+        <v>0.0001642197748878971</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001106616226024926</v>
+        <v>0.0003471492673270404</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002120266726706177</v>
+        <v>0.0005135522806085646</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002860534004867077</v>
+        <v>0.003648831509053707</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0003016575064975768</v>
+        <v>0.0004766953934449703</v>
       </c>
       <c r="H4" t="n">
-        <v>4.908122355118394e-05</v>
+        <v>0.001384336734190583</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001879200135590509</v>
+        <v>0.00046187499538064</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001294837798923254</v>
+        <v>0.001677646534517407</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002245771232992411</v>
+        <v>0.002763255732133985</v>
       </c>
       <c r="L4" t="n">
-        <v>7.665676821488887e-05</v>
+        <v>0.0002157430135412142</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001413680845871568</v>
+        <v>8.23615919216536e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0001782754843588918</v>
+        <v>0.0003935336135327816</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002615283709019423</v>
+        <v>0.003167558927088976</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0001702372392173856</v>
+        <v>0.001525610801763833</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0008006473071873188</v>
+        <v>0.001020291587337852</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0004809105885215104</v>
+        <v>0.0002348114503547549</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0001221904531121254</v>
+        <v>0.0004871347919106483</v>
       </c>
       <c r="T4" t="n">
-        <v>0.000138591683935374</v>
+        <v>0.001553311129100621</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0002534967206884176</v>
+        <v>0.001178893260657787</v>
       </c>
       <c r="V4" t="n">
-        <v>0.000254717975622043</v>
+        <v>0.0006742752739228308</v>
       </c>
       <c r="W4" t="n">
-        <v>9.748000593390316e-05</v>
+        <v>0.001559573807753623</v>
       </c>
       <c r="X4" t="n">
-        <v>0.000184014585101977</v>
+        <v>0.001561663346365094</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0003249140281695873</v>
+        <v>0.001136645907536149</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0002148651255993173</v>
+        <v>0.0006804979639127851</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.418473352212459e-05</v>
+        <v>0.00038521146052517</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0004588981973938644</v>
+        <v>0.000374757481040433</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0005316532915458083</v>
+        <v>0.0003246016276534647</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0002310169802512974</v>
+        <v>0.0008591710939072073</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.0004736172850243747</v>
+        <v>0.0004003540379926562</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0004750699736177921</v>
+        <v>0.0002376340271439403</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0004658814868889749</v>
+        <v>0.000355930533260107</v>
       </c>
       <c r="AH4" t="n">
-        <v>9.242046508006752e-05</v>
+        <v>0.0002419354859739542</v>
       </c>
       <c r="AI4" t="n">
-        <v>9.468577627558261e-05</v>
+        <v>0.001498405705206096</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.0001729374635033309</v>
+        <v>0.0007446741219609976</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.736102032940835e-05</v>
+        <v>4.442757563083433e-05</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0001802036422304809</v>
+        <v>0.0001701972360024229</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0003020140575245023</v>
+        <v>0.0001289508654735982</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.0004880504566244781</v>
+        <v>0.0006832938524894416</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.447645551408641e-05</v>
+        <v>0.001195879420265555</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.000751256593503058</v>
+        <v>0.000728445767890662</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.0005907063605263829</v>
+        <v>0.0005495376535691321</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.0004775743582285941</v>
+        <v>0.0008587538031861186</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.0007098122150637209</v>
+        <v>0.000508412136696279</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.0005254559800960124</v>
+        <v>6.535486318171024e-05</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.002150812651962042</v>
+        <v>0.003390502883121371</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.0005073487991467118</v>
+        <v>0.0005621341988444328</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.584000609815121e-05</v>
+        <v>0.0001667733595240861</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0008793587330728769</v>
+        <v>0.0001125815906561911</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.0009642000077292323</v>
+        <v>0.002437032759189606</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.0005970639758743346</v>
+        <v>0.0003118612803518772</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.0003447182534728199</v>
+        <v>0.0009211633005179465</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.001003611600026488</v>
+        <v>7.36263973522e-06</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.001143941772170365</v>
+        <v>0.001925324788317084</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0004701655125245452</v>
+        <v>0.0001529589208075777</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.0007622643606737256</v>
+        <v>0.0005156946135684848</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.000378850701963529</v>
+        <v>0.0006171645363792777</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.001214344054460526</v>
+        <v>0.0006919576553627849</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.001474709599278867</v>
+        <v>0.0002210286038462073</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.0006270517478697002</v>
+        <v>0.000302746135275811</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.0008926843293011189</v>
+        <v>0.001942082541063428</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.0006580142071470618</v>
+        <v>0.0001542176323710009</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0001379135937895626</v>
+        <v>0.0006535144057124853</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.0004948679124936461</v>
+        <v>0.001068572979420424</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.0001655342057347298</v>
+        <v>0.0001799742167349905</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.001038526184856892</v>
+        <v>0.0001965343835763633</v>
       </c>
       <c r="BP4" t="n">
-        <v>1.086981501430273e-05</v>
+        <v>0.0005563073791563511</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.890080789569765e-05</v>
+        <v>0.000616561621427536</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.0005823174142278731</v>
+        <v>0.0006665950641036034</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.0003232555172871798</v>
+        <v>0.0006788530736230314</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.0002090164634864777</v>
+        <v>0.0001578223018441349</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.0001906483812490478</v>
+        <v>0.0005067590973339975</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.0009722844115458429</v>
+        <v>0.0001519155193818733</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0004773792170453817</v>
+        <v>0.0008799392380751669</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0001371369580738246</v>
+        <v>0.001798228709958494</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.0002168955688830465</v>
+        <v>0.000984465004876256</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.0001210469781653956</v>
+        <v>0.002221166389063001</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.0001983066322281957</v>
+        <v>0.0005765085224993527</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.0003867783816531301</v>
+        <v>0.00030934700043872</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.0004641962586902082</v>
+        <v>0.0004082341329194605</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.365268614492379e-05</v>
+        <v>0.0001086153788492084</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.0006323736743070185</v>
+        <v>0.0005616071866825223</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.000366825086530298</v>
+        <v>0.0002973519440274686</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.0003152078134007752</v>
+        <v>0.0003171645803377032</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.000325717672239989</v>
+        <v>0.0001872339635156095</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.0004596160724759102</v>
+        <v>0.0009038333664648235</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.000209823512705043</v>
+        <v>0.0002573614183347672</v>
       </c>
       <c r="CK4" t="n">
-        <v>7.481845386791974e-06</v>
+        <v>0.0003831307112704962</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.0003170778218191117</v>
+        <v>0.0003048379439860582</v>
       </c>
       <c r="CM4" t="n">
-        <v>9.546623914502561e-05</v>
+        <v>7.254208321683109e-05</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0002148397907149047</v>
+        <v>0.00180916185490787</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.0002831789606716484</v>
+        <v>0.0001480333157815039</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.0007620150572620332</v>
+        <v>0.000536329229362309</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.0002866927243303508</v>
+        <v>0.0007649270701222122</v>
       </c>
       <c r="CR4" t="n">
-        <v>9.526107169222087e-05</v>
+        <v>0.000885531073436141</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.0001965242408914492</v>
+        <v>0.00109429145231843</v>
       </c>
       <c r="CT4" t="n">
-        <v>4.53692045994103e-05</v>
+        <v>0.0009083617478609085</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0005321940989233553</v>
+        <v>0.0001022250507958233</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.730664346017875e-05</v>
+        <v>0.0002237666922155768</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.0005423140828497708</v>
+        <v>0.0004114548210054636</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.0003348504251334816</v>
+        <v>6.855659012217075e-05</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.0004703192680608481</v>
+        <v>0.0003158508043270558</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0004347106441855431</v>
+        <v>0.0003306304861325771</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0004163850098848343</v>
+        <v>0.000784550211392343</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.0001284718455281109</v>
+        <v>0.0002212731633335352</v>
       </c>
       <c r="DC4" t="n">
-        <v>7.242959691211581e-05</v>
+        <v>0.0001443733199266717</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.0003238608478568494</v>
+        <v>0.0001090502919396386</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.0002246108051622286</v>
+        <v>0.0008681498002260923</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.0008869118755683303</v>
+        <v>0.0004104771360289305</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.0001726083282846957</v>
+        <v>0.0004867430252488703</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.0005266686202958226</v>
+        <v>0.0001193374337162822</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.000374206603737548</v>
+        <v>0.0005713748978450894</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.001263221958652139</v>
+        <v>0.001738811959512532</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.000817443709820509</v>
+        <v>0.0003109094977844507</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0006292429170571268</v>
+        <v>0.0008320712950080633</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.00105446542147547</v>
+        <v>0.0006471878732554615</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.0005237571313045919</v>
+        <v>0.0002037703961832449</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.0003387411998119205</v>
+        <v>4.938051279168576e-05</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.0003884302568621933</v>
+        <v>0.0007344823679886758</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0003915311535820365</v>
+        <v>0.0008681928738951683</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.707397162448615e-05</v>
+        <v>0.0003250047448091209</v>
       </c>
       <c r="DS4" t="n">
-        <v>5.610997322946787e-05</v>
+        <v>0.000924357445910573</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.0004775585257448256</v>
+        <v>0.0007358011789619923</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.0001067718403646722</v>
+        <v>8.19822889752686e-06</v>
       </c>
       <c r="DV4" t="n">
-        <v>9.276475611841306e-05</v>
+        <v>0.0001392929116263986</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0001863767975009978</v>
+        <v>0.0004221820272505283</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.0001807893422665074</v>
+        <v>0.0008375843754038215</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.0002872520999517292</v>
+        <v>0.0005102130817249417</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0002545499010011554</v>
+        <v>3.353583451826125e-05</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.0003166494134347886</v>
+        <v>0.0007918202318251133</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.94284220924601e-05</v>
+        <v>1.017460090224631e-05</v>
       </c>
       <c r="EC4" t="n">
-        <v>8.040292595978826e-05</v>
+        <v>0.0001146485374192707</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.0002438958763377741</v>
+        <v>0.001264969818294048</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.0003691171586979181</v>
+        <v>0.001153349643573165</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.0001171088952105492</v>
+        <v>0.0005606752238236368</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.0002582500746939331</v>
+        <v>0.0004708684282377362</v>
       </c>
       <c r="EH4" t="n">
-        <v>8.116509707178921e-05</v>
+        <v>0.0006146490341052413</v>
       </c>
       <c r="EI4" t="n">
-        <v>9.31534159462899e-05</v>
+        <v>6.441370351240039e-05</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.0002600160078145564</v>
+        <v>0.0008119004778563976</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.0002526353055145591</v>
+        <v>0.0008490309701301157</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.0006257948698475957</v>
+        <v>7.238048419822007e-05</v>
       </c>
       <c r="EM4" t="n">
-        <v>4.356335557531565e-05</v>
+        <v>3.888677747454494e-05</v>
       </c>
       <c r="EN4" t="n">
-        <v>4.110588270123117e-05</v>
+        <v>0.0002861494722310454</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.0004824353381991386</v>
+        <v>0.0001332072133664042</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.0002603749162517488</v>
+        <v>7.816294964868575e-05</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.0002013593912124634</v>
+        <v>0.0008918229141272604</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.0005671543767675757</v>
+        <v>0.0003697672800626606</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.000620860664639622</v>
+        <v>0.0004033702425658703</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.001065690303221345</v>
+        <v>0.001262209727428854</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.0002470091567374766</v>
+        <v>4.754704059450887e-05</v>
       </c>
       <c r="EV4" t="n">
-        <v>6.104201747803017e-05</v>
+        <v>0.0002193757973145694</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.0004478763148654252</v>
+        <v>8.988386252894998e-05</v>
       </c>
       <c r="EX4" t="n">
-        <v>1.36015250973287e-05</v>
+        <v>0.0003443932509981096</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.0005603771423920989</v>
+        <v>0.0005366267869248986</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.0001619147806195542</v>
+        <v>1.173781129182316e-05</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.0002693868009373546</v>
+        <v>0.0004054103919770569</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.0004648625035770237</v>
+        <v>0.0005096985842101276</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.0003480789309833199</v>
+        <v>0.0009029689244925976</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.0002922021667473018</v>
+        <v>0.0002677555894479156</v>
       </c>
       <c r="FE4" t="n">
-        <v>3.200418723281473e-05</v>
+        <v>0.0003181719221174717</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.0004953385214321315</v>
+        <v>0.000169057137100026</v>
       </c>
       <c r="FG4" t="n">
-        <v>5.988734483253211e-05</v>
+        <v>0.0005479562096297741</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.0002671712136361748</v>
+        <v>6.597325409529731e-06</v>
       </c>
       <c r="FI4" t="n">
-        <v>4.47996353614144e-05</v>
+        <v>0.0001359693997073919</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.0004123281396459788</v>
+        <v>0.0001562947873026133</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.000361504964530468</v>
+        <v>0.00102072476875037</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.0004010539851151407</v>
+        <v>1.357446308247745e-05</v>
       </c>
       <c r="FM4" t="n">
-        <v>9.317955118604004e-05</v>
+        <v>0.0002403599646640942</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.0005035244976170361</v>
+        <v>0.0003246713895350695</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.0004078600322827697</v>
+        <v>0.0008416996570304036</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.0004372981784399599</v>
+        <v>0.001327032456174493</v>
       </c>
       <c r="FQ4" t="n">
-        <v>4.007050301879644e-05</v>
+        <v>3.911730163963512e-05</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.0002822263049893081</v>
+        <v>0.0005103504518046975</v>
       </c>
       <c r="FS4" t="n">
-        <v>1.854429137893021e-05</v>
+        <v>0.0002126968174707144</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.000554602243937552</v>
+        <v>0.002088720910251141</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.001027223421260715</v>
+        <v>0.0006415338721126318</v>
       </c>
       <c r="FV4" t="n">
-        <v>9.285850683227181e-05</v>
+        <v>0.00134114664979279</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.0005776471807621419</v>
+        <v>0.001184459193609655</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.00018723813991528</v>
+        <v>0.0003468509530648589</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.000596195284742862</v>
+        <v>0.0006382397841662169</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.0006127817323431373</v>
+        <v>0.0006808461621403694</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.000157106842380017</v>
+        <v>0.0003340760013088584</v>
       </c>
       <c r="GB4" t="n">
-        <v>8.760848140809685e-05</v>
+        <v>0.000178121990757063</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.0004048931004945189</v>
+        <v>0.001444554422050714</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.0002842462272383273</v>
+        <v>0.0009314471390098333</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.0003165077359881252</v>
+        <v>0.0003917117428500205</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.0003716300125233829</v>
+        <v>5.36726729478687e-05</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.0001895745226647705</v>
+        <v>0.0002955195377580822</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0002474080247338861</v>
+        <v>0.01492504682391882</v>
       </c>
       <c r="B5" t="n">
-        <v>0.005441668443381786</v>
+        <v>0.05059532076120377</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0005360187496989965</v>
+        <v>0.004742196761071682</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003874510526657104</v>
+        <v>0.07599607110023499</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00255165109410882</v>
+        <v>0.005403531715273857</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001455665566027164</v>
+        <v>0.01401460077613592</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0007843280909582973</v>
+        <v>0.04306020215153694</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0006563448114320636</v>
+        <v>0.0270908996462822</v>
       </c>
       <c r="I5" t="n">
-        <v>3.518685480230488e-05</v>
+        <v>0.02235225029289722</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003121984773315489</v>
+        <v>0.02847231365740299</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003858882235363126</v>
+        <v>0.04805891960859299</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001743194443406537</v>
+        <v>0.005309111438691616</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003656535409390926</v>
+        <v>0.09650740027427673</v>
       </c>
       <c r="N5" t="n">
-        <v>0.004610688425600529</v>
+        <v>0.01448333729058504</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0025078309699893</v>
+        <v>0.02694518119096756</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0001206820306833833</v>
+        <v>0.04129353910684586</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0003174151643179357</v>
+        <v>0.003994953818619251</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0009419807465746999</v>
+        <v>0.02354325354099274</v>
       </c>
       <c r="S5" t="n">
-        <v>0.000117970586870797</v>
+        <v>1.109842560254037e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001202716957777739</v>
+        <v>0.01325179263949394</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0004850936529692262</v>
+        <v>0.00279870186932385</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0003984830691479146</v>
+        <v>0.006916324608027935</v>
       </c>
       <c r="W5" t="n">
-        <v>0.000789462705142796</v>
+        <v>0.009793304838240147</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001429119380190969</v>
+        <v>0.01003305148333311</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001137110055424273</v>
+        <v>0.002376604359596968</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0007475882885046303</v>
+        <v>0.03049854375422001</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.000319340149872005</v>
+        <v>0.006435428280383348</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.000938846031203866</v>
+        <v>0.002911524148657918</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.001022250973619521</v>
+        <v>0.006531387101858854</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0004516329208854586</v>
+        <v>0.002280327025800943</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0007736145635135472</v>
+        <v>0.003956599161028862</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.001567358849570155</v>
+        <v>0.0005969882477074862</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0001035115856211632</v>
+        <v>0.01466662436723709</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.0004565727722365409</v>
+        <v>0.002610292518511415</v>
       </c>
       <c r="AI5" t="n">
-        <v>7.102408562786877e-05</v>
+        <v>0.01543775759637356</v>
       </c>
       <c r="AJ5" t="n">
-        <v>8.615450497018173e-06</v>
+        <v>0.004532660357654095</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.0004685076710302383</v>
+        <v>0.005409325007349253</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0003844674793072045</v>
+        <v>0.008255238644778728</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.000212478480534628</v>
+        <v>0.004963916260749102</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.0002650156966410577</v>
+        <v>0.004031966906040907</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0008788126870058477</v>
+        <v>0.008597444742918015</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.913177250884473e-05</v>
+        <v>0.0098677733913064</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.669567225500941e-05</v>
+        <v>0.01216014008969069</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.838195021264255e-05</v>
+        <v>0.007272947579622269</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.000440501025877893</v>
+        <v>0.003101387294009328</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.0004658313700929284</v>
+        <v>0.001745169749483466</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.004487221129238605</v>
+        <v>0.01349286455661058</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.457611041492783e-05</v>
+        <v>0.0008156765252351761</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.0004295629914849997</v>
+        <v>0.03718851879239082</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.0009016635594889522</v>
+        <v>0.04540485143661499</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.0002998484123963863</v>
+        <v>0.009105101227760315</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0001828511594794691</v>
+        <v>0.001463603461161256</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.0002341577201150358</v>
+        <v>0.004760162904858589</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.248553235200234e-05</v>
+        <v>0.01395478844642639</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0003355863154865801</v>
+        <v>0.01653687283396721</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.0007350100204348564</v>
+        <v>0.01105019543319941</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.001433245488442481</v>
+        <v>0.007448276039212942</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.000678536482155323</v>
+        <v>0.001227596774697304</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.003396777668967843</v>
+        <v>0.02549370750784874</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.001697938423603773</v>
+        <v>0.005538982339203358</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.001239384291693568</v>
+        <v>0.01166839059442282</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.0002549876517150551</v>
+        <v>0.03704066202044487</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.000298596452921629</v>
+        <v>0.006613299716264009</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.0009602243662811816</v>
+        <v>0.00391616253182292</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.0009454977698624134</v>
+        <v>0.01304410584270954</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.0009624207159504294</v>
+        <v>0.005316865630447865</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.0004164382698945701</v>
+        <v>0.01338847074657679</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.001547813415527344</v>
+        <v>0.01563430391252041</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.0004590303578879684</v>
+        <v>0.004812741186469793</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.001247502164915204</v>
+        <v>0.003639244474470615</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.001340667717158794</v>
+        <v>0.004543447867035866</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.0008930278709158301</v>
+        <v>0.01082656066864729</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.0003412197693251073</v>
+        <v>0.001756974263116717</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.002078435383737087</v>
+        <v>0.01435407623648643</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.0005624546902254224</v>
+        <v>0.004642868880182505</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.0005256536533124745</v>
+        <v>0.03213682025671005</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.962504211405758e-05</v>
+        <v>0.007856506854295731</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.0006607040413655341</v>
+        <v>0.007239958271384239</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.0002358407073188573</v>
+        <v>0.006398103665560484</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.0001574015477672219</v>
+        <v>0.008638631552457809</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.0004463302902877331</v>
+        <v>0.008194179274141788</v>
       </c>
       <c r="CD5" t="n">
-        <v>6.769062019884586e-05</v>
+        <v>0.003393296618014574</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.000968653941527009</v>
+        <v>0.009924318641424179</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.0004412893031258136</v>
+        <v>0.002291826996952295</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.0004401521291583776</v>
+        <v>0.02516941539943218</v>
       </c>
       <c r="CH5" t="n">
-        <v>6.308157026069239e-05</v>
+        <v>0.004423101432621479</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.0002972826478071511</v>
+        <v>0.003393256105482578</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.0004270778445061296</v>
+        <v>0.0005258502787910402</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.0001478340709581971</v>
+        <v>0.0017022336833179</v>
       </c>
       <c r="CL5" t="n">
-        <v>5.878995580133051e-05</v>
+        <v>0.002412051893770695</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.001374534680508077</v>
+        <v>0.004519756883382797</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0007046287646517158</v>
+        <v>0.008418276906013489</v>
       </c>
       <c r="CO5" t="n">
-        <v>5.169412361283321e-06</v>
+        <v>0.0164471622556448</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.001796378404833376</v>
+        <v>0.03376153483986855</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.0003854157403111458</v>
+        <v>0.001669486868195236</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.0005823806277476251</v>
+        <v>0.005393136292695999</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.0004729271749965847</v>
+        <v>0.02281822077929974</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.00119388266466558</v>
+        <v>0.01781877875328064</v>
       </c>
       <c r="CU5" t="n">
-        <v>7.124690455384552e-06</v>
+        <v>0.006709896959364414</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.000105254293885082</v>
+        <v>0.003573653986677527</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.000803658738732338</v>
+        <v>0.01088518463075161</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.0005571843939833343</v>
+        <v>0.001327836536802351</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.0005277294549159706</v>
+        <v>0.02693577669560909</v>
       </c>
       <c r="CZ5" t="n">
-        <v>7.702218135818839e-05</v>
+        <v>0.001071009784936905</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.0002380422956775874</v>
+        <v>0.001173526514321566</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.0005125439492985606</v>
+        <v>0.0002493920037522912</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.0002287204406457022</v>
+        <v>0.0006378605030477047</v>
       </c>
       <c r="DD5" t="n">
-        <v>5.809651338495314e-05</v>
+        <v>0.00245426082983613</v>
       </c>
       <c r="DE5" t="n">
-        <v>5.251305992715061e-06</v>
+        <v>0.009385117329657078</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.0004535499319899827</v>
+        <v>0.02226254157721996</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.0001194174983538687</v>
+        <v>0.02261611446738243</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.002353676361963153</v>
+        <v>0.03090724721550941</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.002082977909594774</v>
+        <v>0.02102786675095558</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.0003829219203907996</v>
+        <v>0.004499734379351139</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.0003342406998854131</v>
+        <v>0.003772890660911798</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.0001093687897082418</v>
+        <v>0.02830412238836288</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.000192751525901258</v>
+        <v>0.006052933633327484</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.0002198681759182364</v>
+        <v>0.001369506004266441</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.0004820912436116487</v>
+        <v>0.006752193905413151</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.0004538725188467652</v>
+        <v>0.003867446212098002</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.0004762359312735498</v>
+        <v>0.02337711304426193</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.000490762060508132</v>
+        <v>0.003357922658324242</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.0004999615484848619</v>
+        <v>0.01179973874241114</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.0004397635930217803</v>
+        <v>0.01513273827731609</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.0001604088756721467</v>
+        <v>0.006029156502336264</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.000337190693244338</v>
+        <v>0.02436329051852226</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.0001137495200964622</v>
+        <v>0.002606155583634973</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.0001040214629028924</v>
+        <v>0.006453518755733967</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.0007625485886819661</v>
+        <v>0.000301459978800267</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.0004030424170196056</v>
+        <v>0.003606991376727819</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.0007990180747583508</v>
+        <v>0.007879398763179779</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.001183388871140778</v>
+        <v>0.0008469996973872185</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0006014527752995491</v>
+        <v>0.004864306189119816</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.0007360742310993373</v>
+        <v>0.02826580405235291</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.0001768862566677853</v>
+        <v>0.01571100018918514</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.0001536459312774241</v>
+        <v>0.01244943961501122</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.0007896915194578469</v>
+        <v>0.004008077085018158</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.000131993496324867</v>
+        <v>0.004731323570013046</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.0003825796011369675</v>
+        <v>0.02420167624950409</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.001211831113323569</v>
+        <v>0.006808402948081493</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.0001504373649368063</v>
+        <v>0.006043499801307917</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.001062835450284183</v>
+        <v>0.001657824963331223</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.0006265223491936922</v>
+        <v>0.002120281103998423</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.0003648038837127388</v>
+        <v>0.002692972309887409</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.0001795763964764774</v>
+        <v>0.004974766634404659</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.0006286808638833463</v>
+        <v>0.01786768436431885</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.0004176758229732513</v>
+        <v>0.005113731138408184</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.0002144110767403618</v>
+        <v>0.01226360630244017</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.0002535301318857819</v>
+        <v>0.008686470799148083</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.0009127688826993108</v>
+        <v>0.01949701458215714</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.0007685747696086764</v>
+        <v>0.009850034490227699</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.0003010348882526159</v>
+        <v>0.001820189296267927</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.0002249334065709263</v>
+        <v>0.01018436439335346</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.0001255327515536919</v>
+        <v>0.002702232915908098</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.0008256452274508774</v>
+        <v>0.009107625111937523</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.0003840567660517991</v>
+        <v>0.002588398056104779</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.0005393701721914113</v>
+        <v>0.03148321062326431</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.0003179285849910229</v>
+        <v>0.002123150508850813</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.0004386958607938141</v>
+        <v>0.002580774249508977</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.0004849265969824046</v>
+        <v>0.002207900863140821</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.0001646804303163663</v>
+        <v>0.0009052517125383019</v>
       </c>
       <c r="FF5" t="n">
-        <v>3.055536944884807e-05</v>
+        <v>0.0008267501834779978</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.0002385108382441103</v>
+        <v>0.01063488703221083</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.0001190697512356564</v>
+        <v>0.005614870693534613</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.0001805190113373101</v>
+        <v>0.003846539417281747</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.0008402877720072865</v>
+        <v>0.0151233971118927</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.000318466336466372</v>
+        <v>0.005090790800750256</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.0006935003912076354</v>
+        <v>0.007558505050837994</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.0007138578221201897</v>
+        <v>0.003750311210751534</v>
       </c>
       <c r="FN5" t="n">
-        <v>9.051017696037889e-05</v>
+        <v>0.007750795688480139</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.0003955945721827447</v>
+        <v>0.006132284644991159</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.0007456919411197305</v>
+        <v>0.01693043299019337</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.0001731355005176738</v>
+        <v>0.006982179824262857</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.0005882193217985332</v>
+        <v>0.0003229244612157345</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.0006368269096128643</v>
+        <v>0.026163125410676</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0005906824371777475</v>
+        <v>0.008929919451475143</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.0005250866524875164</v>
+        <v>0.0341479629278183</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.0007276342366822064</v>
+        <v>0.009756882674992085</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.0007491712458431721</v>
+        <v>0.008229681290686131</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.0006887799827381968</v>
+        <v>0.02548119053244591</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.0008279777830466628</v>
+        <v>0.006648615933954716</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.0002660646860022098</v>
+        <v>0.004730469547212124</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.0003407958138268441</v>
+        <v>1.910259015858173e-05</v>
       </c>
       <c r="GB5" t="n">
-        <v>6.154808215796947e-05</v>
+        <v>0.02414757199585438</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.001221275539137423</v>
+        <v>0.003161893459036946</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.0004797128785867244</v>
+        <v>0.005618702154606581</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.001879368093796074</v>
+        <v>0.01738886907696724</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.0001033601511153392</v>
+        <v>0.0001813680864870548</v>
       </c>
       <c r="GG5" t="n">
-        <v>8.397296915063635e-05</v>
+        <v>0.00232247356325388</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.0003071321989409626</v>
+        <v>1.817247047286585e-11</v>
       </c>
       <c r="B6" t="n">
-        <v>0.005077030044049025</v>
+        <v>6.921617723421036e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0002545970492064953</v>
+        <v>1.389317827449332e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001760178827680647</v>
+        <v>9.202414004427784e-12</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002324717352166772</v>
+        <v>4.127317376756423e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001670669298619032</v>
+        <v>7.195384843505792e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00112916948273778</v>
+        <v>8.855922661865634e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>0.000160383788170293</v>
+        <v>8.369587800594047e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0005805335240438581</v>
+        <v>2.044769215059361e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003309821477159858</v>
+        <v>3.012251004186339e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004042719025164843</v>
+        <v>4.072153170220361e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0003351006307639182</v>
+        <v>3.664649417256527e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0022548483684659</v>
+        <v>2.872269644349501e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>0.002817040774971247</v>
+        <v>4.384092533449291e-10</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002096616197377443</v>
+        <v>1.081688849602358e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001857632538303733</v>
+        <v>1.281293737775968e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002102303085848689</v>
+        <v>9.541453183103954e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>0.000647531938739121</v>
+        <v>1.546458516799021e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>7.680066482862458e-05</v>
+        <v>2.149453254274292e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0008210380910895765</v>
+        <v>4.020929977865961e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>6.633020529989153e-05</v>
+        <v>3.547163257566766e-11</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0002349582500755787</v>
+        <v>5.533320468487091e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0004519071953836828</v>
+        <v>6.070545177649933e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0007943717064335942</v>
+        <v>1.222654755217434e-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.351019252790138e-05</v>
+        <v>2.861881287508083e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0001345269265584648</v>
+        <v>9.097319564332906e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.767751645180397e-06</v>
+        <v>2.040869973018999e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0005362082738429308</v>
+        <v>1.050680584202546e-10</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.0007743056048639119</v>
+        <v>4.137979403573411e-10</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0004361968603916466</v>
+        <v>1.070188382357173e-11</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.0006326447473838925</v>
+        <v>2.545447186363958e-10</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.001018708804622293</v>
+        <v>6.721821432797981e-10</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.001308688893914223</v>
+        <v>5.674009595502127e-10</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.0002972743241116405</v>
+        <v>2.037923302333766e-11</v>
       </c>
       <c r="AI6" t="n">
-        <v>7.337654824368656e-05</v>
+        <v>5.59672697075797e-10</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.0004862989590037614</v>
+        <v>1.701226659545085e-11</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.0006599306943826377</v>
+        <v>3.156721412045371e-12</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.0002426817372906953</v>
+        <v>1.995354576012076e-10</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.0001717260456643999</v>
+        <v>4.719721141688282e-11</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.397635787725449e-05</v>
+        <v>3.916375557189156e-10</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.0002185474295401946</v>
+        <v>1.874336102991592e-11</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.0004824103089049459</v>
+        <v>1.296578729798048e-12</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.000788042088970542</v>
+        <v>1.383325398673918e-10</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.005519000813365e-05</v>
+        <v>2.559404424506972e-11</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.0005048693856224418</v>
+        <v>2.782883090635124e-10</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.0009944132762029767</v>
+        <v>1.228264157049352e-10</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.004477144218981266</v>
+        <v>5.966278582292261e-10</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.090804966632277e-05</v>
+        <v>2.448818092748439e-10</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.0009321973193436861</v>
+        <v>2.27926302831527e-10</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.001187098911032081</v>
+        <v>3.154434491392522e-10</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.00137029925826937</v>
+        <v>6.897039050990372e-10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.001365386648103595</v>
+        <v>3.9032690968277e-10</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.001283026300370693</v>
+        <v>6.342757430388701e-10</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.0002124423044733703</v>
+        <v>2.247197844473803e-10</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.000101171295682434</v>
+        <v>1.015990278019352e-10</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.001403321046382189</v>
+        <v>5.865664620685607e-10</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.000943017948884517</v>
+        <v>1.507724084470752e-10</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.0002571264922153205</v>
+        <v>8.109485305496378e-10</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.003268728265538812</v>
+        <v>5.634920308139613e-10</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.00143496529199183</v>
+        <v>3.282570881779634e-10</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.103722701780498e-05</v>
+        <v>1.993039067116342e-10</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.002339065540581942</v>
+        <v>9.264413125542603e-10</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.0004884921945631504</v>
+        <v>3.065828979575969e-10</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.0006203676457516849</v>
+        <v>1.943769034618015e-10</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.00181698624510318</v>
+        <v>2.77042347396339e-11</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.0004863465728703886</v>
+        <v>1.025627360817793e-10</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.0009251692099496722</v>
+        <v>3.356338817983584e-10</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.001599027658812702</v>
+        <v>1.630934276519724e-10</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.0001565598213346675</v>
+        <v>7.965304804624651e-11</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.001040053088217974</v>
+        <v>2.455855518945782e-10</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.0010868035024032</v>
+        <v>3.067023579550465e-10</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.000141531927511096</v>
+        <v>2.356798645131164e-10</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.0004264875897206366</v>
+        <v>5.18619661105113e-11</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.001843152800574899</v>
+        <v>1.912409952620209e-10</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.0006809562328271568</v>
+        <v>5.919126300213406e-12</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.0007953039021231234</v>
+        <v>1.001707272685337e-09</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.0001742081367410719</v>
+        <v>5.706904948610259e-10</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.0002149541105609387</v>
+        <v>4.080831783603855e-10</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.0002823024697136134</v>
+        <v>2.07746542191245e-10</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.0008228010265156627</v>
+        <v>3.065948883662628e-10</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.0001714719401206821</v>
+        <v>3.386540492478218e-10</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.000155802583321929</v>
+        <v>2.367239043676861e-11</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.001050362945534289</v>
+        <v>1.661182476297984e-11</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.0002247188676847145</v>
+        <v>7.74363351219165e-11</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.0005554358940571547</v>
+        <v>6.076864011994587e-11</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.0003138779138680547</v>
+        <v>4.063722969238626e-11</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.211448034155183e-05</v>
+        <v>2.450287750477287e-10</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.0005753013538196683</v>
+        <v>2.064120541156456e-10</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.0003205084940418601</v>
+        <v>1.044541952932576e-10</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.990265445783734e-07</v>
+        <v>2.113002967041311e-10</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.001880872761830688</v>
+        <v>1.985786812763735e-10</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.00171949784271419</v>
+        <v>4.28869190161052e-10</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.0002386087726335973</v>
+        <v>2.35709646245752e-10</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.002188308630138636</v>
+        <v>8.311296095797616e-12</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.00125312153249979</v>
+        <v>8.495930070573365e-10</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.0002665976644493639</v>
+        <v>3.969052517205363e-11</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.0003076131106354296</v>
+        <v>6.316315803722716e-10</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.0008516318048350513</v>
+        <v>4.710057344148311e-10</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.0001942497037816793</v>
+        <v>6.98531926746071e-11</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.0001733048702590168</v>
+        <v>3.714795832054918e-11</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.0008019228116609156</v>
+        <v>1.965179234619807e-11</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.0003583927173167467</v>
+        <v>5.798465180228973e-11</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.0008431558380834758</v>
+        <v>7.527235085236228e-11</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.0003851719957310706</v>
+        <v>1.374248492780339e-10</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.000112943205749616</v>
+        <v>2.900893691926143e-10</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.0004937678459100425</v>
+        <v>2.015973776803293e-10</v>
       </c>
       <c r="DC6" t="n">
-        <v>6.47251436021179e-05</v>
+        <v>1.247537489978967e-10</v>
       </c>
       <c r="DD6" t="n">
-        <v>8.584439638070762e-05</v>
+        <v>2.156571310418798e-10</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.001072792452760041</v>
+        <v>5.340288211641564e-10</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.001738602528348565</v>
+        <v>1.072559485670865e-09</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.0004709800996351987</v>
+        <v>5.329605090587108e-10</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.001171614974737167</v>
+        <v>3.868816100816019e-10</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.0008110828930512071</v>
+        <v>2.491446771113459e-10</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.001947229728102684</v>
+        <v>1.00723795970481e-09</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.002475850516930223</v>
+        <v>2.689123923538261e-10</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.0008013850310817361</v>
+        <v>5.064935693077643e-10</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.001526667037978768</v>
+        <v>3.015496186087319e-10</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.0004775434790644795</v>
+        <v>2.881748173422238e-10</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.0008098211255855858</v>
+        <v>1.139394342764e-10</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.0008404544787481427</v>
+        <v>1.748998168515925e-10</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.0002482730196788907</v>
+        <v>5.687528226161476e-10</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.0004135054186917841</v>
+        <v>5.018384596766623e-10</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.0003684389812406152</v>
+        <v>3.517468954994385e-11</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.001093794940970838</v>
+        <v>2.425810941009132e-10</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.0002127101179212332</v>
+        <v>2.319339997836067e-10</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.0006668538553640246</v>
+        <v>3.834873044117337e-11</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.0003636295441538095</v>
+        <v>2.079361405282754e-10</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.0001120233719120733</v>
+        <v>5.722730067603266e-10</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.0001239319972228259</v>
+        <v>7.366489362947704e-12</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.568459164351225e-05</v>
+        <v>4.727647162638959e-10</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.0005378618370741606</v>
+        <v>2.762738371409057e-10</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.0002089889894705266</v>
+        <v>2.382989916505096e-10</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.0002750195271801203</v>
+        <v>2.861447745416967e-10</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.0007454658043570817</v>
+        <v>3.531122338973347e-10</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.0005265422514639795</v>
+        <v>1.436319951864107e-10</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.0002786263357847929</v>
+        <v>1.393722498521655e-10</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.00034146654070355</v>
+        <v>1.001048272053495e-10</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.0001156838770839386</v>
+        <v>8.867998002592969e-11</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.0006751787732355297</v>
+        <v>3.387501668061788e-10</v>
       </c>
       <c r="EJ6" t="n">
-        <v>1.200296537717804e-05</v>
+        <v>2.243189245465516e-10</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.000986939063295722</v>
+        <v>1.945658079094414e-10</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.001064935466274619</v>
+        <v>1.133146354526104e-11</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.0001793033006833866</v>
+        <v>1.197775819500313e-11</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.0001170728501165286</v>
+        <v>3.893750044614563e-10</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.0009469154756516218</v>
+        <v>9.882587109766305e-11</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.0001183813001262024</v>
+        <v>3.118061919771264e-10</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.0005694408318959177</v>
+        <v>1.043589034632753e-10</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.0006276839994825423</v>
+        <v>2.166486851029603e-10</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.0009808212053030729</v>
+        <v>7.060773632439066e-10</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.0007166746072471142</v>
+        <v>2.481533867282337e-10</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.0008622371824458241</v>
+        <v>1.300263646752953e-10</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.0001083206516341306</v>
+        <v>9.221171048956478e-11</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.0003227491397410631</v>
+        <v>4.775355111341639e-11</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.0001531619054730982</v>
+        <v>4.275391499164449e-11</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.0006876936531625688</v>
+        <v>2.160875992029965e-11</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.0001535700284875929</v>
+        <v>6.224474408123015e-11</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.0003721195680554956</v>
+        <v>4.036975614907234e-11</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.0003902729949913919</v>
+        <v>4.715639684294004e-11</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.0001282765879295766</v>
+        <v>2.620756389681844e-10</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.0006909514777362347</v>
+        <v>2.284622213633014e-10</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.0001020117342704907</v>
+        <v>8.185255251369483e-11</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.0003346282464917749</v>
+        <v>1.555307826972552e-10</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.0005866656429134309</v>
+        <v>6.052422452107464e-10</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.0004588393203448504</v>
+        <v>2.843405233488028e-10</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.0002228739904239774</v>
+        <v>1.776263303110426e-10</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.0008715033764019608</v>
+        <v>1.889512157848827e-10</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.0007546350243501365</v>
+        <v>7.012448954846207e-11</v>
       </c>
       <c r="FL6" t="n">
-        <v>8.801594958640635e-06</v>
+        <v>7.645618860241399e-11</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.0007112227031029761</v>
+        <v>1.901780954938204e-10</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.0005234941490925848</v>
+        <v>3.87036569460264e-10</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.0005207907524891198</v>
+        <v>3.146030380651865e-10</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.001571000902913511</v>
+        <v>1.460368076466878e-10</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.0001597727386979386</v>
+        <v>6.969113064414501e-10</v>
       </c>
       <c r="FR6" t="n">
-        <v>7.509443094022572e-06</v>
+        <v>5.538884906286512e-10</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.0007578174700029194</v>
+        <v>1.664126614286943e-10</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.000947454129345715</v>
+        <v>3.696974393285757e-10</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.00101508991792798</v>
+        <v>1.306181413029961e-10</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.0001191204646602273</v>
+        <v>8.328191469786361e-10</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.0003527773078531027</v>
+        <v>3.040648843821714e-10</v>
       </c>
       <c r="FX6" t="n">
-        <v>7.247063331305981e-05</v>
+        <v>6.502722665890914e-11</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.0007793548866175115</v>
+        <v>2.052785025297155e-10</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.001303634722717106</v>
+        <v>6.215912506934984e-11</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.0004884860827587545</v>
+        <v>1.237595997904961e-10</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.0006853823433630168</v>
+        <v>1.922793591013772e-10</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.001167103415355086</v>
+        <v>3.31582983292833e-10</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.0005099367699585855</v>
+        <v>5.129443536588951e-10</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.0002742141950875521</v>
+        <v>3.047823451951537e-11</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.001183338928967714</v>
+        <v>3.412372606703684e-10</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.0006028725765645504</v>
+        <v>3.128991232781431e-10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3.035987239385918e-09</v>
+        <v>3.445582857455908e-16</v>
       </c>
       <c r="B7" t="n">
-        <v>1.776423674826333e-09</v>
+        <v>2.892553140369444e-15</v>
       </c>
       <c r="C7" t="n">
-        <v>1.918129655109624e-09</v>
+        <v>2.269228158990346e-15</v>
       </c>
       <c r="D7" t="n">
-        <v>1.779420721881309e-09</v>
+        <v>5.042987681364453e-15</v>
       </c>
       <c r="E7" t="n">
-        <v>1.403082372508635e-10</v>
+        <v>6.467689051833187e-15</v>
       </c>
       <c r="F7" t="n">
-        <v>1.659184567515126e-09</v>
+        <v>1.493095638717846e-14</v>
       </c>
       <c r="G7" t="n">
-        <v>2.113978103679415e-09</v>
+        <v>6.481877277216171e-17</v>
       </c>
       <c r="H7" t="n">
-        <v>8.148952623798777e-10</v>
+        <v>4.070207610892568e-15</v>
       </c>
       <c r="I7" t="n">
-        <v>2.607163374079846e-10</v>
+        <v>1.869035118730669e-14</v>
       </c>
       <c r="J7" t="n">
-        <v>1.38471589750111e-09</v>
+        <v>1.287263074996672e-15</v>
       </c>
       <c r="K7" t="n">
-        <v>1.001805749467621e-09</v>
+        <v>1.646068433739257e-14</v>
       </c>
       <c r="L7" t="n">
-        <v>2.379855867928882e-09</v>
+        <v>1.451731144727685e-15</v>
       </c>
       <c r="M7" t="n">
-        <v>2.199355142451509e-09</v>
+        <v>9.120740661751163e-15</v>
       </c>
       <c r="N7" t="n">
-        <v>6.524031093135818e-09</v>
+        <v>6.187546880572457e-15</v>
       </c>
       <c r="O7" t="n">
-        <v>4.3227549317848e-10</v>
+        <v>1.609597905535918e-14</v>
       </c>
       <c r="P7" t="n">
-        <v>2.696998180340415e-10</v>
+        <v>3.903303156767898e-15</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.22743409775228e-09</v>
+        <v>6.851592335616096e-15</v>
       </c>
       <c r="R7" t="n">
-        <v>1.011250194693503e-09</v>
+        <v>1.427789567891129e-14</v>
       </c>
       <c r="S7" t="n">
-        <v>1.887545120204948e-10</v>
+        <v>3.599713842977748e-15</v>
       </c>
       <c r="T7" t="n">
-        <v>4.750693172184128e-10</v>
+        <v>7.855246333498926e-15</v>
       </c>
       <c r="U7" t="n">
-        <v>9.169209835846459e-10</v>
+        <v>3.450232433061624e-15</v>
       </c>
       <c r="V7" t="n">
-        <v>1.332946975018956e-09</v>
+        <v>1.06181915744772e-14</v>
       </c>
       <c r="W7" t="n">
-        <v>4.733397562795005e-10</v>
+        <v>1.762979986877442e-14</v>
       </c>
       <c r="X7" t="n">
-        <v>3.288407324220088e-09</v>
+        <v>7.413652482711475e-15</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.827215267979909e-09</v>
+        <v>2.32541143086525e-15</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.442228500131876e-10</v>
+        <v>4.370485025858954e-15</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.862879236597564e-10</v>
+        <v>4.703049642708779e-15</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.057117449132505e-10</v>
+        <v>4.900552738536538e-15</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.682478766364738e-10</v>
+        <v>1.935530000298858e-15</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.126437692595573e-09</v>
+        <v>4.439748180505359e-15</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.570256008027627e-09</v>
+        <v>1.035480159733079e-14</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.831200080459894e-09</v>
+        <v>6.519991112864654e-16</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.137883121060668e-09</v>
+        <v>4.63194461491857e-15</v>
       </c>
       <c r="AH7" t="n">
-        <v>7.210804731094811e-10</v>
+        <v>3.578628651821746e-15</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.303197549873403e-10</v>
+        <v>9.721958718481635e-15</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.604987143188907e-09</v>
+        <v>3.035160454402126e-15</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.286070028250208e-09</v>
+        <v>4.246152871179758e-15</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.767686245799041e-11</v>
+        <v>2.734541685157996e-15</v>
       </c>
       <c r="AM7" t="n">
-        <v>4.7713993867049e-10</v>
+        <v>2.305251834962361e-15</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.248178449486659e-09</v>
+        <v>9.773266892228617e-15</v>
       </c>
       <c r="AO7" t="n">
-        <v>2.674849453043748e-09</v>
+        <v>6.031349769934028e-15</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.711956409966575e-10</v>
+        <v>1.582647498264125e-15</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8.453772126770787e-10</v>
+        <v>2.97564580194567e-16</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.731179088970691e-09</v>
+        <v>2.026640252237319e-15</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.172207413941862e-10</v>
+        <v>2.283280435585295e-15</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.085973226430895e-10</v>
+        <v>3.386892368057132e-15</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.122292894872317e-09</v>
+        <v>2.038210637593518e-14</v>
       </c>
       <c r="AV7" t="n">
-        <v>7.114835942623188e-10</v>
+        <v>3.963475530307896e-15</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.578792817648946e-11</v>
+        <v>5.983714754562814e-15</v>
       </c>
       <c r="AX7" t="n">
-        <v>2.15591677843463e-09</v>
+        <v>2.360418455542323e-15</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.901758306388501e-09</v>
+        <v>1.664142549822711e-15</v>
       </c>
       <c r="AZ7" t="n">
-        <v>8.582017319014312e-10</v>
+        <v>2.655837077765021e-15</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.548907668791344e-10</v>
+        <v>5.79602961762668e-15</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.438826918194081e-09</v>
+        <v>6.272500897050275e-15</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.325846321620361e-09</v>
+        <v>1.928095009785655e-16</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.315308276327869e-10</v>
+        <v>4.259699045588723e-15</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.399841020877091e-09</v>
+        <v>3.07056346698204e-15</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.580713642785781e-09</v>
+        <v>6.001249183603926e-15</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.631649260147583e-09</v>
+        <v>2.576337318192811e-15</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.662044415075343e-10</v>
+        <v>9.384737114487805e-15</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.669052756587575e-10</v>
+        <v>6.097929100687058e-15</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1.845465336103302e-09</v>
+        <v>8.29000632246793e-15</v>
       </c>
       <c r="BK7" t="n">
-        <v>2.654202635454794e-09</v>
+        <v>5.21656929621233e-15</v>
       </c>
       <c r="BL7" t="n">
-        <v>7.376316224494417e-11</v>
+        <v>7.255046410371054e-15</v>
       </c>
       <c r="BM7" t="n">
-        <v>3.530692183062456e-09</v>
+        <v>7.064090032192624e-15</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.299325978036507e-10</v>
+        <v>2.807807070480178e-15</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.094893176123435e-09</v>
+        <v>1.028289527637248e-15</v>
       </c>
       <c r="BP7" t="n">
-        <v>7.606532292925294e-09</v>
+        <v>8.20707671473405e-15</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.686041084525414e-09</v>
+        <v>5.72193541056561e-15</v>
       </c>
       <c r="BR7" t="n">
-        <v>1.075985300857951e-09</v>
+        <v>1.267926668063572e-14</v>
       </c>
       <c r="BS7" t="n">
-        <v>3.877651977290952e-09</v>
+        <v>9.014836132355958e-16</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.045519557711486e-10</v>
+        <v>1.319763199787228e-15</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.606011210801398e-10</v>
+        <v>2.920817571028136e-15</v>
       </c>
       <c r="BV7" t="n">
-        <v>3.331068754164335e-09</v>
+        <v>3.656343077699381e-15</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.344306191508053e-10</v>
+        <v>5.527814517296238e-15</v>
       </c>
       <c r="BX7" t="n">
-        <v>1.398471116687006e-09</v>
+        <v>1.260322175669713e-14</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.68757063878644e-09</v>
+        <v>1.152730187236987e-14</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.339105715203459e-09</v>
+        <v>8.30349362808706e-15</v>
       </c>
       <c r="CA7" t="n">
-        <v>2.206625548950569e-09</v>
+        <v>1.46125730076898e-15</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.141168519211647e-10</v>
+        <v>7.375848555242568e-15</v>
       </c>
       <c r="CC7" t="n">
-        <v>1.733059362685196e-09</v>
+        <v>1.093942373752571e-14</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.082615829264057e-10</v>
+        <v>3.149168124487239e-15</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.009497208048771e-10</v>
+        <v>1.160131052910327e-15</v>
       </c>
       <c r="CF7" t="n">
-        <v>1.007020578036588e-10</v>
+        <v>6.585182474254489e-16</v>
       </c>
       <c r="CG7" t="n">
-        <v>9.59976986791844e-10</v>
+        <v>2.233278810159453e-15</v>
       </c>
       <c r="CH7" t="n">
-        <v>4.590521018865701e-10</v>
+        <v>5.361752966833203e-16</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.540726518063252e-10</v>
+        <v>2.337939048155141e-15</v>
       </c>
       <c r="CJ7" t="n">
-        <v>5.788283186092258e-10</v>
+        <v>2.304955373430822e-15</v>
       </c>
       <c r="CK7" t="n">
-        <v>2.501285567557687e-10</v>
+        <v>2.009258924401424e-15</v>
       </c>
       <c r="CL7" t="n">
-        <v>6.593189327830373e-10</v>
+        <v>4.648233905527217e-15</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.542679178318963e-09</v>
+        <v>3.055078857673284e-15</v>
       </c>
       <c r="CN7" t="n">
-        <v>3.717162799787843e-09</v>
+        <v>1.083294491979227e-14</v>
       </c>
       <c r="CO7" t="n">
-        <v>6.849038558520704e-10</v>
+        <v>5.294788659605647e-16</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.952568995378101e-09</v>
+        <v>5.730624274538545e-15</v>
       </c>
       <c r="CQ7" t="n">
-        <v>5.184314755268815e-09</v>
+        <v>5.313032796377438e-15</v>
       </c>
       <c r="CR7" t="n">
-        <v>7.228834197903211e-11</v>
+        <v>4.415074957784789e-15</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.600658577378567e-10</v>
+        <v>3.633480387903567e-15</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.080116967562162e-09</v>
+        <v>2.821760879495008e-15</v>
       </c>
       <c r="CU7" t="n">
-        <v>3.943982085363729e-10</v>
+        <v>5.069080954821096e-15</v>
       </c>
       <c r="CV7" t="n">
-        <v>4.049206456246957e-11</v>
+        <v>3.734335330383715e-15</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.001367599950953e-10</v>
+        <v>1.356928358534786e-15</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.108898806112535e-10</v>
+        <v>4.547247143544652e-16</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.032624430408191e-09</v>
+        <v>2.691126587930004e-15</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.385509567659483e-10</v>
+        <v>5.462992462271405e-16</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.286592581945968e-10</v>
+        <v>2.99511358368889e-15</v>
       </c>
       <c r="DB7" t="n">
-        <v>4.415709464744566e-10</v>
+        <v>1.428367964339161e-15</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.264338911344254e-10</v>
+        <v>9.982001644936967e-16</v>
       </c>
       <c r="DD7" t="n">
-        <v>1.844203678658118e-10</v>
+        <v>4.152032264146755e-15</v>
       </c>
       <c r="DE7" t="n">
-        <v>4.537681785876657e-09</v>
+        <v>1.314521018755789e-15</v>
       </c>
       <c r="DF7" t="n">
-        <v>4.784302287674791e-09</v>
+        <v>6.269197892072456e-15</v>
       </c>
       <c r="DG7" t="n">
-        <v>5.800488978024987e-10</v>
+        <v>6.831217805102841e-15</v>
       </c>
       <c r="DH7" t="n">
-        <v>5.778581613213873e-09</v>
+        <v>3.274401310464077e-15</v>
       </c>
       <c r="DI7" t="n">
-        <v>2.578608659931092e-09</v>
+        <v>3.437106704631853e-16</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.74310360484742e-10</v>
+        <v>8.86480542157354e-15</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.46356951400162e-09</v>
+        <v>2.970403938551587e-15</v>
       </c>
       <c r="DL7" t="n">
-        <v>3.946004856203444e-09</v>
+        <v>4.784984410246109e-15</v>
       </c>
       <c r="DM7" t="n">
-        <v>4.033912093248659e-10</v>
+        <v>3.123837815957836e-15</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.279017225463974e-09</v>
+        <v>2.43534021379286e-15</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.922468850779069e-10</v>
+        <v>6.684193214250228e-16</v>
       </c>
       <c r="DP7" t="n">
-        <v>1.316765252390439e-09</v>
+        <v>2.802076045559055e-15</v>
       </c>
       <c r="DQ7" t="n">
-        <v>2.114386443707872e-11</v>
+        <v>9.956901094094507e-15</v>
       </c>
       <c r="DR7" t="n">
-        <v>1.471293642474336e-09</v>
+        <v>4.322886856420946e-15</v>
       </c>
       <c r="DS7" t="n">
-        <v>1.233762647601111e-09</v>
+        <v>6.329683667802939e-15</v>
       </c>
       <c r="DT7" t="n">
-        <v>2.960772516047427e-09</v>
+        <v>5.066018507200298e-15</v>
       </c>
       <c r="DU7" t="n">
-        <v>1.330682564137931e-09</v>
+        <v>2.782435680852833e-15</v>
       </c>
       <c r="DV7" t="n">
-        <v>2.962495526670494e-10</v>
+        <v>7.322290132592087e-16</v>
       </c>
       <c r="DW7" t="n">
-        <v>4.080529247829645e-10</v>
+        <v>4.453498066338138e-15</v>
       </c>
       <c r="DX7" t="n">
-        <v>3.715732721509823e-10</v>
+        <v>2.295267434096601e-15</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.095742882157197e-10</v>
+        <v>3.509891504635586e-15</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.200643889338494e-09</v>
+        <v>6.405676922731753e-15</v>
       </c>
       <c r="EA7" t="n">
-        <v>3.085013633441491e-10</v>
+        <v>2.461468850875051e-15</v>
       </c>
       <c r="EB7" t="n">
-        <v>2.63497057506612e-10</v>
+        <v>5.147914311222053e-15</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.278384731406845e-09</v>
+        <v>5.967035405281956e-15</v>
       </c>
       <c r="ED7" t="n">
-        <v>1.655362846797459e-09</v>
+        <v>3.04259465082194e-15</v>
       </c>
       <c r="EE7" t="n">
-        <v>4.153307697762898e-10</v>
+        <v>9.115135421222708e-16</v>
       </c>
       <c r="EF7" t="n">
-        <v>3.601213494075495e-10</v>
+        <v>3.045660063058053e-15</v>
       </c>
       <c r="EG7" t="n">
-        <v>1.811009675556363e-09</v>
+        <v>1.71739148781009e-15</v>
       </c>
       <c r="EH7" t="n">
-        <v>5.289745308445504e-10</v>
+        <v>1.422301858478061e-16</v>
       </c>
       <c r="EI7" t="n">
-        <v>2.781176622335124e-09</v>
+        <v>5.300593694030535e-15</v>
       </c>
       <c r="EJ7" t="n">
-        <v>1.211893363439742e-10</v>
+        <v>2.25552189535435e-15</v>
       </c>
       <c r="EK7" t="n">
-        <v>1.109423330980519e-09</v>
+        <v>1.284560828136694e-15</v>
       </c>
       <c r="EL7" t="n">
-        <v>6.366459581741424e-10</v>
+        <v>2.040409196311412e-15</v>
       </c>
       <c r="EM7" t="n">
-        <v>1.714467318114643e-10</v>
+        <v>2.994058180636611e-15</v>
       </c>
       <c r="EN7" t="n">
-        <v>5.669056335477762e-10</v>
+        <v>5.214591474280491e-15</v>
       </c>
       <c r="EO7" t="n">
-        <v>8.776225857154429e-10</v>
+        <v>1.277465656654019e-15</v>
       </c>
       <c r="EP7" t="n">
-        <v>3.315033803019674e-10</v>
+        <v>4.092519729272668e-15</v>
       </c>
       <c r="EQ7" t="n">
-        <v>5.180168793916806e-11</v>
+        <v>4.120521367959474e-15</v>
       </c>
       <c r="ER7" t="n">
-        <v>9.923545318812899e-10</v>
+        <v>1.65618446352502e-16</v>
       </c>
       <c r="ES7" t="n">
-        <v>6.954197773190174e-10</v>
+        <v>1.962950150867374e-15</v>
       </c>
       <c r="ET7" t="n">
-        <v>6.058887280779857e-10</v>
+        <v>5.342797110627481e-15</v>
       </c>
       <c r="EU7" t="n">
-        <v>4.985072354912745e-10</v>
+        <v>5.417004396587009e-15</v>
       </c>
       <c r="EV7" t="n">
-        <v>2.964620771095383e-10</v>
+        <v>4.117856602307412e-15</v>
       </c>
       <c r="EW7" t="n">
-        <v>2.149581068700002e-10</v>
+        <v>4.422245091683296e-15</v>
       </c>
       <c r="EX7" t="n">
-        <v>2.300269558164203e-10</v>
+        <v>4.695896449469217e-15</v>
       </c>
       <c r="EY7" t="n">
-        <v>1.944388816621512e-10</v>
+        <v>2.18689041552836e-15</v>
       </c>
       <c r="EZ7" t="n">
-        <v>1.280592576424766e-10</v>
+        <v>2.965576697785185e-16</v>
       </c>
       <c r="FA7" t="n">
-        <v>7.865001427909135e-10</v>
+        <v>1.51406091118434e-15</v>
       </c>
       <c r="FB7" t="n">
-        <v>2.408856170088569e-10</v>
+        <v>2.862525345933247e-16</v>
       </c>
       <c r="FC7" t="n">
-        <v>1.019426099091447e-09</v>
+        <v>2.613982003467634e-15</v>
       </c>
       <c r="FD7" t="n">
-        <v>5.083650167492237e-10</v>
+        <v>3.130419473716239e-15</v>
       </c>
       <c r="FE7" t="n">
-        <v>4.18187900974587e-10</v>
+        <v>1.840007765496385e-15</v>
       </c>
       <c r="FF7" t="n">
-        <v>1.388800185964101e-10</v>
+        <v>5.007371639998304e-15</v>
       </c>
       <c r="FG7" t="n">
-        <v>7.350127173566534e-10</v>
+        <v>9.362383915009764e-15</v>
       </c>
       <c r="FH7" t="n">
-        <v>1.235871627258689e-09</v>
+        <v>2.953540359604701e-15</v>
       </c>
       <c r="FI7" t="n">
-        <v>2.620249295315347e-10</v>
+        <v>3.519679817374057e-15</v>
       </c>
       <c r="FJ7" t="n">
-        <v>8.969925913149268e-10</v>
+        <v>2.612165117795774e-15</v>
       </c>
       <c r="FK7" t="n">
-        <v>4.08971190246632e-10</v>
+        <v>7.628151612263246e-16</v>
       </c>
       <c r="FL7" t="n">
-        <v>6.117848450060137e-10</v>
+        <v>8.665688304464788e-15</v>
       </c>
       <c r="FM7" t="n">
-        <v>1.844138175499666e-10</v>
+        <v>8.511585059271971e-15</v>
       </c>
       <c r="FN7" t="n">
-        <v>1.018770179328499e-09</v>
+        <v>8.574367353080697e-16</v>
       </c>
       <c r="FO7" t="n">
-        <v>7.357965348120388e-10</v>
+        <v>3.650526078934112e-15</v>
       </c>
       <c r="FP7" t="n">
-        <v>8.49644965494889e-10</v>
+        <v>2.679483273037046e-15</v>
       </c>
       <c r="FQ7" t="n">
-        <v>3.764171641051917e-09</v>
+        <v>9.580986178037154e-15</v>
       </c>
       <c r="FR7" t="n">
-        <v>9.300136216694455e-10</v>
+        <v>4.086417703920648e-15</v>
       </c>
       <c r="FS7" t="n">
-        <v>1.18658483039269e-09</v>
+        <v>9.242201798255641e-15</v>
       </c>
       <c r="FT7" t="n">
-        <v>1.301143748300149e-09</v>
+        <v>2.376821460324139e-15</v>
       </c>
       <c r="FU7" t="n">
-        <v>1.614351208267806e-09</v>
+        <v>7.463051655953582e-16</v>
       </c>
       <c r="FV7" t="n">
-        <v>1.692364914873679e-09</v>
+        <v>8.080923862734731e-15</v>
       </c>
       <c r="FW7" t="n">
-        <v>5.600117036763663e-10</v>
+        <v>7.493475173594825e-15</v>
       </c>
       <c r="FX7" t="n">
-        <v>6.89718504531811e-10</v>
+        <v>6.625915229896764e-15</v>
       </c>
       <c r="FY7" t="n">
-        <v>3.422500616245827e-10</v>
+        <v>4.004570180776885e-15</v>
       </c>
       <c r="FZ7" t="n">
-        <v>2.583424141278101e-09</v>
+        <v>3.848654708593418e-15</v>
       </c>
       <c r="GA7" t="n">
-        <v>1.945057892527302e-09</v>
+        <v>1.443012846359833e-15</v>
       </c>
       <c r="GB7" t="n">
-        <v>1.922482173455364e-09</v>
+        <v>2.3512131132298e-16</v>
       </c>
       <c r="GC7" t="n">
-        <v>1.251040382399538e-09</v>
+        <v>1.724465906985558e-15</v>
       </c>
       <c r="GD7" t="n">
-        <v>2.86720069908597e-09</v>
+        <v>8.475245651768867e-15</v>
       </c>
       <c r="GE7" t="n">
-        <v>1.66642355470259e-09</v>
+        <v>2.754428324693633e-16</v>
       </c>
       <c r="GF7" t="n">
-        <v>1.834308926973449e-09</v>
+        <v>5.303937356589822e-15</v>
       </c>
       <c r="GG7" t="n">
-        <v>3.647055990541048e-10</v>
+        <v>3.747995854240559e-15</v>
       </c>
     </row>
     <row r="8">
@@ -4982,3416 +4982,3416 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.0004757003043778241</v>
+        <v>0.01877268590033054</v>
       </c>
       <c r="B9" t="n">
-        <v>0.008834927342832088</v>
+        <v>0.08347716927528381</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001265270169824362</v>
+        <v>0.002614401280879974</v>
       </c>
       <c r="D9" t="n">
-        <v>0.004772200714796782</v>
+        <v>0.2252597212791443</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0005554129602387547</v>
+        <v>0.0073395068757236</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001327514182776213</v>
+        <v>0.09119835495948792</v>
       </c>
       <c r="G9" t="n">
-        <v>0.000639726931694895</v>
+        <v>0.1352496594190598</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001185958390124142</v>
+        <v>0.1130135655403137</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001588397135492414</v>
+        <v>0.02228761464357376</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001146467868238688</v>
+        <v>0.02745789289474487</v>
       </c>
       <c r="K9" t="n">
-        <v>0.006360914092510939</v>
+        <v>0.05351929366588593</v>
       </c>
       <c r="L9" t="n">
-        <v>4.689315028372221e-05</v>
+        <v>0.01702357456088066</v>
       </c>
       <c r="M9" t="n">
-        <v>0.004433211870491505</v>
+        <v>0.3378623723983765</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001815716503188014</v>
+        <v>0.03422608971595764</v>
       </c>
       <c r="O9" t="n">
-        <v>0.002124357968568802</v>
+        <v>0.1240708529949188</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0002364723477512598</v>
+        <v>0.1567847281694412</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0002641232858877629</v>
+        <v>0.02525370195508003</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001136663486249745</v>
+        <v>0.04097900912165642</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0002845863637048751</v>
+        <v>0.006102860439568758</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001290799584239721</v>
+        <v>0.01248849742114544</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0002432675391901284</v>
+        <v>0.02348634600639343</v>
       </c>
       <c r="V9" t="n">
-        <v>0.00099631876219064</v>
+        <v>0.04634528979659081</v>
       </c>
       <c r="W9" t="n">
-        <v>2.319971827091649e-05</v>
+        <v>0.06513123214244843</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0008311421843245625</v>
+        <v>0.04318870976567268</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0008641517488285899</v>
+        <v>0.005900764837861061</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0004335917765274644</v>
+        <v>0.01641465537250042</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0005595075199380517</v>
+        <v>0.01325027644634247</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0006546992808580399</v>
+        <v>0.01174612529575825</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.002101126359775662</v>
+        <v>0.03938738256692886</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22541532618925e-05</v>
+        <v>0.02775905281305313</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.0004865142109338194</v>
+        <v>0.03231021761894226</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.000780407921411097</v>
+        <v>0.03426851332187653</v>
       </c>
       <c r="AG9" t="n">
-        <v>5.190539013710804e-05</v>
+        <v>0.05022548884153366</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0001437144237570465</v>
+        <v>0.02730073966085911</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.0002488910395186394</v>
+        <v>0.05875574797391891</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.0003594677546061575</v>
+        <v>0.05428758263587952</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0003666837874334306</v>
+        <v>0.01809544488787651</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0009519687155261636</v>
+        <v>0.05912484973669052</v>
       </c>
       <c r="AM9" t="n">
-        <v>9.1270383563824e-05</v>
+        <v>0.04168550670146942</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.0004861097841057926</v>
+        <v>0.05237701907753944</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.0009370188927277923</v>
+        <v>0.02003682404756546</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.001258728909306228</v>
+        <v>0.04413049295544624</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.0001541503588669002</v>
+        <v>0.03704804182052612</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.348592923022807e-05</v>
+        <v>0.03855261951684952</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.0004701119614765048</v>
+        <v>0.01421827170997858</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.0009566633380018175</v>
+        <v>0.03103694319725037</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.006563181057572365</v>
+        <v>0.1067532598972321</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.00034930175752379</v>
+        <v>0.06462427228689194</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.001024592551402748</v>
+        <v>0.1047995463013649</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0009862694423645735</v>
+        <v>0.1589054763317108</v>
       </c>
       <c r="AY9" t="n">
-        <v>2.97377300739754e-05</v>
+        <v>0.09399047493934631</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.0002579378196969628</v>
+        <v>0.005743858404457569</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.675562665099278e-05</v>
+        <v>0.00937812402844429</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.0003358070680405945</v>
+        <v>0.03816810995340347</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.737353159114718e-05</v>
+        <v>0.003969475626945496</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.001397694926708937</v>
+        <v>0.02426907047629356</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.001755109755322337</v>
+        <v>0.0005346015095710754</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.0003387499018572271</v>
+        <v>0.003396689891815186</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.002919780556112528</v>
+        <v>0.0725477933883667</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.001596001791767776</v>
+        <v>0.006590916775166988</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.001272153574973345</v>
+        <v>0.01885953731834888</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.0007824889617040753</v>
+        <v>0.04181429743766785</v>
       </c>
       <c r="BK9" t="n">
-        <v>3.532094706315547e-05</v>
+        <v>0.04344367235898972</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0009512240067124367</v>
+        <v>0.003104574047029018</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.001421216526068747</v>
+        <v>0.03991536796092987</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.0008909340249374509</v>
+        <v>0.002197547117248178</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.0001341521274298429</v>
+        <v>0.01640157401561737</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.001228187931701541</v>
+        <v>0.01632401347160339</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.0005712807178497314</v>
+        <v>0.02944161184132099</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.0005565170431509614</v>
+        <v>0.07772834599018097</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.0004515584150794894</v>
+        <v>0.003104544710367918</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.0006379885016940534</v>
+        <v>0.01396070886403322</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.0006745310965925455</v>
+        <v>0.01544686779379845</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.003076849039644003</v>
+        <v>0.0711839571595192</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.001007916056551039</v>
+        <v>0.03651639446616173</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.0008592843078076839</v>
+        <v>0.1226870268583298</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0006841433933004737</v>
+        <v>0.05263185873627663</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.001290147891268134</v>
+        <v>0.06735610961914062</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.0003485959023237228</v>
+        <v>0.02445736899971962</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.0002107857872033492</v>
+        <v>0.001921231625601649</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.0008366513648070395</v>
+        <v>0.01315190270543098</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.0003545791551005095</v>
+        <v>0.02601426094770432</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.001592238317243755</v>
+        <v>0.02260374836623669</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.000505354255437851</v>
+        <v>0.0006538847228512168</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.0005435219500213861</v>
+        <v>0.07337147742509842</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.0004496184119489044</v>
+        <v>0.0005032502231188118</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.0002042622654698789</v>
+        <v>0.001572463079355657</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.0001840167824411765</v>
+        <v>0.01696373149752617</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.0001516045449534431</v>
+        <v>0.03375642746686935</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.0003004030149895698</v>
+        <v>0.008062107488512993</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.001489593996666372</v>
+        <v>0.05744144320487976</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.0008737806929275393</v>
+        <v>0.01467092894017696</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.000338357116561383</v>
+        <v>0.07718978822231293</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.002005392918363214</v>
+        <v>0.1414764523506165</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.0004511118750087917</v>
+        <v>0.03071613609790802</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.0009651635773479939</v>
+        <v>0.003756878897547722</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.0006165110389702022</v>
+        <v>0.04639188945293427</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.001595028792507946</v>
+        <v>0.02786767855286598</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.0002106363535858691</v>
+        <v>0.02896909043192863</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0003386965836398304</v>
+        <v>0.02600145153701305</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.001270287204533815</v>
+        <v>0.01712706685066223</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.0006919715669937432</v>
+        <v>0.005867629777640104</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.0008648062357679009</v>
+        <v>0.08453778177499771</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0002632573305163532</v>
+        <v>0.01354481838643551</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.0002129889617208391</v>
+        <v>0.005385732278227806</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.0003280041855759919</v>
+        <v>0.01976614817976952</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.0002933065989054739</v>
+        <v>0.03149832785129547</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.000211854072404094</v>
+        <v>0.01609888859093189</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.0005827047862112522</v>
+        <v>0.03832454234361649</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.001412880956195295</v>
+        <v>0.03534684330224991</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.000508785480633378</v>
+        <v>0.008284111507236958</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.001494816271588206</v>
+        <v>0.05680739879608154</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.000950078887399286</v>
+        <v>0.02259678393602371</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.0008858470246195793</v>
+        <v>0.07866039872169495</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.000867180700879544</v>
+        <v>0.008225060999393463</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.0005431594327092171</v>
+        <v>0.1212802454829216</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.0001878678885987028</v>
+        <v>0.04565336182713509</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.0006068787188269198</v>
+        <v>0.001135606318712234</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.000161686388310045</v>
+        <v>0.02614283934235573</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.0006328690215013921</v>
+        <v>0.01707298308610916</v>
       </c>
       <c r="DQ9" t="n">
-        <v>2.980148565256968e-05</v>
+        <v>0.008397229015827179</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.000946897198446095</v>
+        <v>0.009921858087182045</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.0005755426245741546</v>
+        <v>0.006405385211110115</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.0005562203004956245</v>
+        <v>0.008905811235308647</v>
       </c>
       <c r="DU9" t="n">
-        <v>6.591425335500389e-05</v>
+        <v>0.04548266530036926</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.0007987458957359195</v>
+        <v>0.07180678099393845</v>
       </c>
       <c r="DW9" t="n">
-        <v>3.084381751250476e-05</v>
+        <v>0.007591895759105682</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0004185622092336416</v>
+        <v>0.001215908443555236</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.001008591847494245</v>
+        <v>0.06621911376714706</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.0001311722007812932</v>
+        <v>0.06290532648563385</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.001497559482231736</v>
+        <v>0.00850355252623558</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.0008779211202636361</v>
+        <v>0.03745922073721886</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.0002068410540232435</v>
+        <v>0.03062923438847065</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.0001407541567459702</v>
+        <v>0.06672924011945724</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0001922975643537939</v>
+        <v>0.05314984172582626</v>
       </c>
       <c r="EF9" t="n">
-        <v>8.395902113988996e-05</v>
+        <v>0.05811963230371475</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.0009115683496929705</v>
+        <v>0.0146973729133606</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.0003326061414554715</v>
+        <v>0.03253129124641418</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.0006553985876962543</v>
+        <v>0.07212704420089722</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.0006805000593885779</v>
+        <v>0.001449146308004856</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.0001730609074002132</v>
+        <v>0.008811595849692822</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.000487089972011745</v>
+        <v>0.00295345252379775</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.0003079472226090729</v>
+        <v>0.02136901579797268</v>
       </c>
       <c r="EN9" t="n">
-        <v>4.966773121850565e-05</v>
+        <v>0.01137873530387878</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.0004215092048980296</v>
+        <v>0.01619731262326241</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.00145602785050869</v>
+        <v>0.03722547367215157</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.0003869005886372179</v>
+        <v>0.0005929199978709221</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.00082682870561257</v>
+        <v>0.07469716668128967</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0004083530220668763</v>
+        <v>0.01898831315338612</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.0009617740288376808</v>
+        <v>0.02665898390114307</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.0009527216898277402</v>
+        <v>0.04170992225408554</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0003107591765001416</v>
+        <v>0.02311971783638</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.0003514891723170877</v>
+        <v>0.07994417101144791</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.000101807432656642</v>
+        <v>0.02801653370261192</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.001360882306471467</v>
+        <v>0.02534071728587151</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.0003223094681743532</v>
+        <v>0.002007506554946303</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.0007458148174919188</v>
+        <v>0.09075154364109039</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.0001742087479215115</v>
+        <v>0.001469499431550503</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.0003984635113738477</v>
+        <v>0.009174708276987076</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.0004148453299421817</v>
+        <v>0.02713689580559731</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.0001908191479742527</v>
+        <v>0.0380534753203392</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.0003662736562546343</v>
+        <v>0.005907661747187376</v>
       </c>
       <c r="FG9" t="n">
-        <v>8.778923074714839e-06</v>
+        <v>0.003384806914255023</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.000294468569336459</v>
+        <v>0.001340716145932674</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.0004964761319570243</v>
+        <v>0.02303132228553295</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.0006959050660952926</v>
+        <v>0.02343009412288666</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.0008114571101032197</v>
+        <v>0.03113807365298271</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.0009975258726626635</v>
+        <v>0.000367429107427597</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.0001037623587762937</v>
+        <v>0.01308433059602976</v>
       </c>
       <c r="FN9" t="n">
-        <v>5.785110261058435e-05</v>
+        <v>0.04727645963430405</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.0005549733177758753</v>
+        <v>0.02769400551915169</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.0004909569397568703</v>
+        <v>0.05577380582690239</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.0003496363351587206</v>
+        <v>0.08806987851858139</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.0005376752815209329</v>
+        <v>0.07590891420841217</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.000880930689163506</v>
+        <v>0.09676480293273926</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.0009383873548358679</v>
+        <v>0.05871909856796265</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.0002386322303209454</v>
+        <v>0.0414077490568161</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.0002078504476230592</v>
+        <v>0.04102072864770889</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.0009497205610387027</v>
+        <v>0.13423091173172</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.0004778321599587798</v>
+        <v>0.003754214383661747</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.001066491473466158</v>
+        <v>0.02554153650999069</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.000579899875447154</v>
+        <v>0.03603704646229744</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.0003212415613234043</v>
+        <v>0.03112858533859253</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.0004152330802753568</v>
+        <v>0.08406253904104233</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.0008938138489611447</v>
+        <v>0.02586191892623901</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.001269704080186784</v>
+        <v>0.04443470761179924</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.002167029539123178</v>
+        <v>0.08803939074277878</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.0004341081657912582</v>
+        <v>0.01591477915644646</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.0004587145813275129</v>
+        <v>0.02016811817884445</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.008982026018202305</v>
+        <v>0.1640453785657883</v>
       </c>
       <c r="B10" t="n">
-        <v>0.07476583123207092</v>
+        <v>0.00157698430120945</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01055107731372118</v>
+        <v>0.02837381511926651</v>
       </c>
       <c r="D10" t="n">
-        <v>0.03581808134913445</v>
+        <v>0.8494081497192383</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002866887953132391</v>
+        <v>0.1781910210847855</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0119422422721982</v>
+        <v>0.05135810375213623</v>
       </c>
       <c r="G10" t="n">
-        <v>0.007292349822819233</v>
+        <v>0.5098308324813843</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0002347344416193664</v>
+        <v>0.3066421151161194</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001267667859792709</v>
+        <v>0.2832643091678619</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01420522108674049</v>
+        <v>0.1458239853382111</v>
       </c>
       <c r="K10" t="n">
-        <v>0.05019188299775124</v>
+        <v>0.3438847661018372</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001502024126239121</v>
+        <v>0.009754990227520466</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04188520461320877</v>
+        <v>1.268427133560181</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01811774075031281</v>
+        <v>0.4597077369689941</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02202890813350677</v>
+        <v>0.03442759439349174</v>
       </c>
       <c r="P10" t="n">
-        <v>0.005106458906084299</v>
+        <v>0.5717308521270752</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.008410939015448093</v>
+        <v>0.182160884141922</v>
       </c>
       <c r="R10" t="n">
-        <v>0.002031057374551892</v>
+        <v>0.3379111289978027</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0008872647304087877</v>
+        <v>0.05014605075120926</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01563003845512867</v>
+        <v>0.0527784638106823</v>
       </c>
       <c r="U10" t="n">
-        <v>0.007673740386962891</v>
+        <v>0.002717754570767283</v>
       </c>
       <c r="V10" t="n">
-        <v>0.005551733076572418</v>
+        <v>0.1737747937440872</v>
       </c>
       <c r="W10" t="n">
-        <v>0.001755284145474434</v>
+        <v>0.2052998840808868</v>
       </c>
       <c r="X10" t="n">
-        <v>0.009111203253269196</v>
+        <v>0.03309911489486694</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.005857695825397968</v>
+        <v>0.02786287479102612</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.004857013933360577</v>
+        <v>0.01790348812937737</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.004959485493600368</v>
+        <v>0.01299213897436857</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.01002527587115765</v>
+        <v>0.01304306834936142</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.01360766403377056</v>
+        <v>0.03210146352648735</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.002366314176470041</v>
+        <v>0.01050060894340277</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.008188414387404919</v>
+        <v>0.04943131655454636</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0009805244626477361</v>
+        <v>0.05107065662741661</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.0005675717256963253</v>
+        <v>0.2031205296516418</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.00669056037440896</v>
+        <v>0.1417611241340637</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.0006905984482727945</v>
+        <v>0.00194220244884491</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.001173008349724114</v>
+        <v>0.1553750336170197</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.009757685475051403</v>
+        <v>0.104387529194355</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.005870350636541843</v>
+        <v>0.302799254655838</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.005808597430586815</v>
+        <v>0.0355321504175663</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.007113522849977016</v>
+        <v>0.1872300803661346</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.005125285126268864</v>
+        <v>0.08621122688055038</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.003966697957366705</v>
+        <v>0.02393894270062447</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.00182672415394336</v>
+        <v>0.2877909541130066</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.004661960992962122</v>
+        <v>0.02475140988826752</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.003452432341873646</v>
+        <v>0.006790796294808388</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.005394048057496548</v>
+        <v>0.3099732995033264</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.06069452315568924</v>
+        <v>0.1917490065097809</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.00250936159864068</v>
+        <v>0.1288550943136215</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.004014389123767614</v>
+        <v>0.3045846223831177</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.01260001212358475</v>
+        <v>0.538835346698761</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.002812543651089072</v>
+        <v>0.03125976398587227</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.0001668836921453476</v>
+        <v>0.04836589097976685</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.001134900376200676</v>
+        <v>0.0166565515100956</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.005199773702770472</v>
+        <v>0.2085971981287003</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.0007717488333582878</v>
+        <v>0.02997317910194397</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.01243423298001289</v>
+        <v>0.1209945157170296</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.01265543326735497</v>
+        <v>0.006112465634942055</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.006197653710842133</v>
+        <v>0.05789429694414139</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.02602008171379566</v>
+        <v>0.005418911576271057</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.01030822098255157</v>
+        <v>0.03446229547262192</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.003046184312552214</v>
+        <v>0.2307920455932617</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.008126367814838886</v>
+        <v>0.02970648370683193</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.0003769775212276727</v>
+        <v>0.1704563945531845</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.01489500422030687</v>
+        <v>0.06227347254753113</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.01811284385621548</v>
+        <v>0.03848948702216148</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.0082247294485569</v>
+        <v>0.0170638058334589</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.007074336521327496</v>
+        <v>0.2046452462673187</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.007809155154973269</v>
+        <v>0.08459830284118652</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.003034465480595827</v>
+        <v>0.07121425122022629</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.0005956731038168073</v>
+        <v>0.04347798600792885</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.001899154973216355</v>
+        <v>0.08661638200283051</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.002507466590031981</v>
+        <v>0.04215925186872482</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.005200378596782684</v>
+        <v>0.0526728667318821</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.02761601842939854</v>
+        <v>0.08599467575550079</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.004726207815110683</v>
+        <v>0.08119118958711624</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.002360868267714977</v>
+        <v>0.6078189015388489</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.008674405515193939</v>
+        <v>0.3173120319843292</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.01115400157868862</v>
+        <v>0.08381893485784531</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.003884459612891078</v>
+        <v>0.04454827308654785</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.002703153761103749</v>
+        <v>0.03645195066928864</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.004877977538853884</v>
+        <v>0.06727106124162674</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.003673389554023743</v>
+        <v>0.05065866559743881</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.01405723206698895</v>
+        <v>0.03034501150250435</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.002934067044407129</v>
+        <v>0.03700023144483566</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.002026990056037903</v>
+        <v>0.3135652244091034</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.006804715376347303</v>
+        <v>0.06647142022848129</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.000723190198186785</v>
+        <v>0.0459032841026783</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.002658547135069966</v>
+        <v>0.0314611978828907</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.0005638962611556053</v>
+        <v>0.1094973161816597</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.002529586665332317</v>
+        <v>0.03170270845293999</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.01565380208194256</v>
+        <v>0.1281199753284454</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.01640262268483639</v>
+        <v>0.06303626298904419</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.005817891098558903</v>
+        <v>0.1568747758865356</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.0198068805038929</v>
+        <v>0.4100994467735291</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.01150340866297483</v>
+        <v>0.3729671537876129</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.01365976780653</v>
+        <v>0.1436615884304047</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.008384956046938896</v>
+        <v>0.2212850451469421</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.008919502608478069</v>
+        <v>0.02643699944019318</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.001811550348065794</v>
+        <v>0.1939861625432968</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.00364044145680964</v>
+        <v>0.04998233541846275</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.01220244728028774</v>
+        <v>0.04380903765559196</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.00389726972207427</v>
+        <v>0.04567393660545349</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.005847577936947346</v>
+        <v>0.3428925275802612</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.007582567632198334</v>
+        <v>0.08274777233600616</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.002215276239439845</v>
+        <v>0.04178688675165176</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.002065527252852917</v>
+        <v>0.01222138479351997</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.0006322775734588504</v>
+        <v>0.09231423586606979</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.002164077712222934</v>
+        <v>0.04597800970077515</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.001536148018203676</v>
+        <v>0.2358299046754837</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.008857906796038151</v>
+        <v>0.006651058793067932</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.002988566178828478</v>
+        <v>0.2953954339027405</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.01245098188519478</v>
+        <v>0.4305758476257324</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.003331293817609549</v>
+        <v>0.1587088406085968</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.004724764730781317</v>
+        <v>0.2691142559051514</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.007828887552022934</v>
+        <v>0.004135427996516228</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.001272600842639804</v>
+        <v>0.3729890286922455</v>
       </c>
       <c r="DM10" t="n">
-        <v>5.527411121875048e-05</v>
+        <v>0.03422977775335312</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.006433677393943071</v>
+        <v>0.0858871266245842</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.002557871863245964</v>
+        <v>0.006248938385397196</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.005930210463702679</v>
+        <v>0.07205303013324738</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.001976750558242202</v>
+        <v>0.004650406539440155</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.003197781275957823</v>
+        <v>0.0028191227465868</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.002347595989704132</v>
+        <v>0.05547516793012619</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.0001563436817377806</v>
+        <v>0.09291872382164001</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.001369094243273139</v>
+        <v>0.1485623121261597</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.002125099301338196</v>
+        <v>0.3120979070663452</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.002770178020000458</v>
+        <v>0.09618061780929565</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.001745735644362867</v>
+        <v>0.02668482810258865</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.01132396422326565</v>
+        <v>0.2505149841308594</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.001553096575662494</v>
+        <v>0.1278794407844543</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.0074837994761765</v>
+        <v>0.032294861972332</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.003822654252871871</v>
+        <v>0.2042665630578995</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.0006303875125013292</v>
+        <v>0.04358309879899025</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.002201694762334228</v>
+        <v>0.3014687597751617</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.0004163183621130884</v>
+        <v>0.03477774187922478</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.005225755739957094</v>
+        <v>0.1947827488183975</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.01480180025100708</v>
+        <v>0.1173011884093285</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.002698692958801985</v>
+        <v>0.03692346066236496</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.00464971037581563</v>
+        <v>0.3464459180831909</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.0004946445696987212</v>
+        <v>0.04314213618636131</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.002204279880970716</v>
+        <v>0.01721376180648804</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.0001195546647068113</v>
+        <v>0.05872166901826859</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.002204024698585272</v>
+        <v>0.03839487582445145</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.003369608661159873</v>
+        <v>0.08190623670816422</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.003723952453583479</v>
+        <v>0.009288489818572998</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.009068797342479229</v>
+        <v>0.08410691469907761</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.001127151073887944</v>
+        <v>0.05528855323791504</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.005432647187262774</v>
+        <v>0.3575560450553894</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.01049964968115091</v>
+        <v>0.1922045797109604</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.001751971081830561</v>
+        <v>0.2164575010538101</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.00592015078291297</v>
+        <v>0.06156726181507111</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.007358684670180082</v>
+        <v>0.1300856620073318</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.001184292603284121</v>
+        <v>0.2054668515920639</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.001625288394279778</v>
+        <v>0.05104244500398636</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.01385525334626436</v>
+        <v>0.01894900016486645</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.002155109075829387</v>
+        <v>0.008508171886205673</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.003199227852746844</v>
+        <v>0.36240553855896</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.003712525591254234</v>
+        <v>0.08648604899644852</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.002302326261997223</v>
+        <v>0.01373733580112457</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.002985445549711585</v>
+        <v>0.008371211588382721</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.0002506235614418983</v>
+        <v>0.1206970661878586</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.003363306634128094</v>
+        <v>0.03921208158135414</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.00487183453515172</v>
+        <v>0.04299106448888779</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.003242241917178035</v>
+        <v>0.04036381468176842</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.002017514314502478</v>
+        <v>0.004381138831377029</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.006293801590800285</v>
+        <v>0.1652224361896515</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.005287713371217251</v>
+        <v>0.05079267919063568</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.003703400492668152</v>
+        <v>0.06898535788059235</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.002846413990482688</v>
+        <v>0.09979717433452606</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.00480343634262681</v>
+        <v>0.05009482800960541</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.002613947261124849</v>
+        <v>0.1569148600101471</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.004035347141325474</v>
+        <v>0.0948011726140976</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.01099022757261992</v>
+        <v>0.1429917365312576</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.001946411095559597</v>
+        <v>0.04502631723880768</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.01131100486963987</v>
+        <v>0.1392400115728378</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.00109948730096221</v>
+        <v>0.1938981562852859</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.0004222014686092734</v>
+        <v>0.09385262429714203</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.003651238745078444</v>
+        <v>0.06300164759159088</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.001922036521136761</v>
+        <v>0.3380487859249115</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.001898457761853933</v>
+        <v>0.1811961829662323</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.01239787880331278</v>
+        <v>0.01578955352306366</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.007801373489201069</v>
+        <v>0.01557764410972595</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.002365272026509047</v>
+        <v>0.14533431828022</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.000291042379103601</v>
+        <v>0.2863825559616089</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.008141135796904564</v>
+        <v>0.1468186378479004</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.006523382849991322</v>
+        <v>0.002551287412643433</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.01574083045125008</v>
+        <v>0.1370546519756317</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.005626721773296595</v>
+        <v>0.02465640567243099</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.00245154881849885</v>
+        <v>0.1166563853621483</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.001048332545906305</v>
+        <v>0.009252100251615047</v>
       </c>
       <c r="B11" t="n">
-        <v>0.04481512680649757</v>
+        <v>0.1459803283214569</v>
       </c>
       <c r="C11" t="n">
-        <v>0.003143827663734555</v>
+        <v>0.03785883635282516</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0159689299762249</v>
+        <v>0.05845966190099716</v>
       </c>
       <c r="E11" t="n">
-        <v>0.004281772300601006</v>
+        <v>0.06354685127735138</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03804579377174377</v>
+        <v>0.1935466676950455</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00351585098542273</v>
+        <v>0.02702955901622772</v>
       </c>
       <c r="H11" t="n">
-        <v>0.02294359728693962</v>
+        <v>0.1191599145531654</v>
       </c>
       <c r="I11" t="n">
-        <v>0.00233503757044673</v>
+        <v>0.007837247103452682</v>
       </c>
       <c r="J11" t="n">
-        <v>0.008460747078061104</v>
+        <v>0.01992160081863403</v>
       </c>
       <c r="K11" t="n">
-        <v>0.04183859750628471</v>
+        <v>0.1843796223402023</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001747194677591324</v>
+        <v>0.06117505580186844</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01041529700160027</v>
+        <v>0.0008764676749706268</v>
       </c>
       <c r="N11" t="n">
-        <v>0.005635736044496298</v>
+        <v>0.1310445070266724</v>
       </c>
       <c r="O11" t="n">
-        <v>0.03165052458643913</v>
+        <v>0.2189537137746811</v>
       </c>
       <c r="P11" t="n">
-        <v>0.002812402322888374</v>
+        <v>0.027192622423172</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01052585616707802</v>
+        <v>0.05236353352665901</v>
       </c>
       <c r="R11" t="n">
-        <v>0.008469263091683388</v>
+        <v>0.01737443916499615</v>
       </c>
       <c r="S11" t="n">
-        <v>0.001910663209855556</v>
+        <v>0.009722155518829823</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0003879631403833628</v>
+        <v>0.03645893186330795</v>
       </c>
       <c r="U11" t="n">
-        <v>0.002380425808951259</v>
+        <v>0.01891343668103218</v>
       </c>
       <c r="V11" t="n">
-        <v>0.005154379177838564</v>
+        <v>0.05055980384349823</v>
       </c>
       <c r="W11" t="n">
-        <v>0.01900402642786503</v>
+        <v>0.05159982666373253</v>
       </c>
       <c r="X11" t="n">
-        <v>0.007819836959242821</v>
+        <v>0.032753586769104</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.00274684140458703</v>
+        <v>0.003761169500648975</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.009562601335346699</v>
+        <v>0.01142446510493755</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.005473589990288019</v>
+        <v>0.01451894454658031</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.000884530832991004</v>
+        <v>0.01358248945325613</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.002181353745982051</v>
+        <v>0.02052197605371475</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0008888918673619628</v>
+        <v>0.009898293763399124</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0003940633032470942</v>
+        <v>0.02636873349547386</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0005281706107780337</v>
+        <v>0.07261656224727631</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.003723956644535065</v>
+        <v>0.06768397986888885</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.0001982426038011909</v>
+        <v>0.03084928914904594</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0004292703233659267</v>
+        <v>0.1116551980376244</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.0004905634559690952</v>
+        <v>0.02162757329642773</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.006056243553757668</v>
+        <v>0.02332364022731781</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.004822444170713425</v>
+        <v>0.04763960093259811</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.0003539748722687364</v>
+        <v>0.02702015452086926</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.004452074877917767</v>
+        <v>0.01572523638606071</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.0001500567304901779</v>
+        <v>0.01093247532844543</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.009451223537325859</v>
+        <v>0.01913697645068169</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.002164337318390608</v>
+        <v>0.02194581925868988</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.001075232867151499</v>
+        <v>0.01432288251817226</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.004305559210479259</v>
+        <v>0.002416116651147604</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.001211093738675117</v>
+        <v>0.007890822365880013</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.02613512054085732</v>
+        <v>0.2158065140247345</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.0003373966319486499</v>
+        <v>0.05785998329520226</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.007921789772808552</v>
+        <v>0.001776506658643484</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.002271338598802686</v>
+        <v>0.09790772944688797</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.0269299577921629</v>
+        <v>0.1410999894142151</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.009851155802607536</v>
+        <v>0.02730726078152657</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.001695339800789952</v>
+        <v>0.02968817390501499</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.006992679089307785</v>
+        <v>0.008551488630473614</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.000223216600716114</v>
+        <v>0.008175252936780453</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.01659950613975525</v>
+        <v>0.04885293543338776</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.01114508509635925</v>
+        <v>0.03500545024871826</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.001226764637976885</v>
+        <v>0.05002956464886665</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.002485311590135098</v>
+        <v>0.004206746816635132</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.01191037241369486</v>
+        <v>0.01654536463320255</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.005922628566622734</v>
+        <v>0.01228156685829163</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.0005413175676949322</v>
+        <v>0.07713650912046432</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.004931875038892031</v>
+        <v>0.04556475579738617</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.00380455213598907</v>
+        <v>0.01700441911816597</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.01007190346717834</v>
+        <v>0.05977513641119003</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.003797714598476887</v>
+        <v>0.003834361210465431</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.005482257343828678</v>
+        <v>0.01313841342926025</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.001453752629458904</v>
+        <v>0.05352700129151344</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.00124471471644938</v>
+        <v>0.05515866354107857</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.002982734004035592</v>
+        <v>0.04547666013240814</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.006639949977397919</v>
+        <v>0.005348244216293097</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.001868288149125874</v>
+        <v>0.0423874706029892</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.0012558086309582</v>
+        <v>0.02880314737558365</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.0146982129663229</v>
+        <v>0.1301413476467133</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.002849624026566744</v>
+        <v>0.0198871698230505</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.004371830727905035</v>
+        <v>0.07539044320583344</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.0005342221120372415</v>
+        <v>0.04601453617215157</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.008992239832878113</v>
+        <v>0.07515676319599152</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.001654960215091705</v>
+        <v>0.006043190136551857</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.0004560757661238313</v>
+        <v>0.0008536016102880239</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.003587273648008704</v>
+        <v>0.0229814313352108</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.0004679720150306821</v>
+        <v>0.00330218905583024</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.006237168330699205</v>
+        <v>0.05376796424388885</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.004086185246706009</v>
+        <v>0.006676536984741688</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.001104990602470934</v>
+        <v>0.008341995999217033</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.0001100310691981576</v>
+        <v>0.01655672863125801</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.005187217146158218</v>
+        <v>0.04293929412961006</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.004004429094493389</v>
+        <v>0.008579010143876076</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.006287298630923033</v>
+        <v>0.01049784943461418</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.00411814171820879</v>
+        <v>0.01272967178374529</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.005929841194301844</v>
+        <v>0.04164278879761696</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.005313501227647066</v>
+        <v>0.07727053016424179</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.001499670092016459</v>
+        <v>0.07329873740673065</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.01056316308677197</v>
+        <v>0.09326009452342987</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.003401740919798613</v>
+        <v>0.05291124805808067</v>
       </c>
       <c r="CR11" t="n">
-        <v>2.464302815496922e-05</v>
+        <v>0.007039849646389484</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.01027022954076529</v>
+        <v>0.03336915746331215</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.003512066323310137</v>
+        <v>0.01801860518753529</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.0042470907792449</v>
+        <v>0.0147358812391758</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.0002497674431651831</v>
+        <v>0.008890740573406219</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.005684823729097843</v>
+        <v>0.0420251302421093</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.003683704184368253</v>
+        <v>0.01467251777648926</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.002561160828918219</v>
+        <v>0.001285478472709656</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.001487545901909471</v>
+        <v>0.02750951051712036</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.004176774527877569</v>
+        <v>0.04968246072530746</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.003371804021298885</v>
+        <v>0.0006117401644587517</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.008494308218359947</v>
+        <v>0.004150324035435915</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.003434366546571255</v>
+        <v>0.008578703738749027</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.006349892355501652</v>
+        <v>0.01838506199419498</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.0008709620451554656</v>
+        <v>0.02851570770144463</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.001946095027960837</v>
+        <v>0.009621521458029747</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.01972678303718567</v>
+        <v>0.007401447743177414</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.01142695359885693</v>
+        <v>0.004029795527458191</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.01392419170588255</v>
+        <v>0.01355030573904514</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.006346730515360832</v>
+        <v>0.00910637341439724</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.005620374344289303</v>
+        <v>0.08988525718450546</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.01331969164311886</v>
+        <v>0.07905103266239166</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.001572633860632777</v>
+        <v>0.00641092611476779</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.0007454785518348217</v>
+        <v>0.01604585908353329</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.004348518792539835</v>
+        <v>0.01357911713421345</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.002251528901979327</v>
+        <v>0.03271696716547012</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.008293768391013145</v>
+        <v>0.004174262750893831</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.00143956346437335</v>
+        <v>0.001440160907804966</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.002700106240808964</v>
+        <v>0.007034639362245798</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.001153810415416956</v>
+        <v>0.03899521380662918</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.001064182142727077</v>
+        <v>0.02148867398500443</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.0005714003345929086</v>
+        <v>0.01296231430023909</v>
       </c>
       <c r="DX11" t="n">
-        <v>8.073581557255238e-05</v>
+        <v>0.02094905450940132</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.0005024243146181107</v>
+        <v>0.04654808342456818</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.004624415189027786</v>
+        <v>0.009213253855705261</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.006717170588672161</v>
+        <v>0.0550658255815506</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.00603549275547266</v>
+        <v>0.02619380503892899</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.0008231387473642826</v>
+        <v>0.01802901923656464</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.002585227601230145</v>
+        <v>0.005567295011132956</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.00812160037457943</v>
+        <v>0.04392273351550102</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.0003724289126694202</v>
+        <v>0.005187412723898888</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.007041281554847956</v>
+        <v>0.002951973117887974</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.002979464828968048</v>
+        <v>0.01801430620253086</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.003907297737896442</v>
+        <v>0.0003822334110736847</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.0006395092350430787</v>
+        <v>0.008277371525764465</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.0007744843605905771</v>
+        <v>0.02983295172452927</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.002994795562699437</v>
+        <v>0.0114367613568902</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.004520037211477757</v>
+        <v>0.01047428697347641</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.003641416784375906</v>
+        <v>0.0007708163466304541</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.0001475784229114652</v>
+        <v>0.005363454110920429</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.003674102248623967</v>
+        <v>0.04052876681089401</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.002622692380100489</v>
+        <v>0.01221961155533791</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.002919132355600595</v>
+        <v>0.01550744194537401</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.0002887957962229848</v>
+        <v>0.03772999718785286</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.00448063388466835</v>
+        <v>0.02384311147034168</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.007634466513991356</v>
+        <v>0.007773164659738541</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.01779407449066639</v>
+        <v>0.03825186192989349</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.001369824865832925</v>
+        <v>0.04112562909722328</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.0002040434628725052</v>
+        <v>0.0007724319584667683</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.005230258218944073</v>
+        <v>0.05771016702055931</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.00253049866296351</v>
+        <v>0.007460310123860836</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.0005891016917303205</v>
+        <v>0.001854453235864639</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.000380105571821332</v>
+        <v>0.0173700638115406</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.003911517094820738</v>
+        <v>0.04321198910474777</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.006147363223135471</v>
+        <v>0.01250823587179184</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.008057919330894947</v>
+        <v>0.005419505294412374</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.005134907551109791</v>
+        <v>0.008670809678733349</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.002539224689826369</v>
+        <v>0.001765152905136347</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.001806186977773905</v>
+        <v>0.03143462166190147</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.000398511765524745</v>
+        <v>0.03225405514240265</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.01063141599297523</v>
+        <v>0.04503606632351875</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.0009740903042256832</v>
+        <v>0.03249460831284523</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.003579207230359316</v>
+        <v>0.04446050152182579</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.005456015467643738</v>
+        <v>0.02377690374851227</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.001216419273987412</v>
+        <v>0.1031149625778198</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.0009207096882164478</v>
+        <v>0.07779716700315475</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.004366256762295961</v>
+        <v>0.0102396821603179</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.007218779064714909</v>
+        <v>0.06786612421274185</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.004796588327735662</v>
+        <v>0.03088151663541794</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.003698911517858505</v>
+        <v>0.07092087715864182</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.01987564936280251</v>
+        <v>0.01340682432055473</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.01076522283256054</v>
+        <v>0.04284923151135445</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.008566188625991344</v>
+        <v>0.01841764152050018</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.001785553060472012</v>
+        <v>0.1742613911628723</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.001946259755641222</v>
+        <v>0.01754634641110897</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.006750787608325481</v>
+        <v>0.01517070736736059</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.00206860015168786</v>
+        <v>0.003942461684346199</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.000604020431637764</v>
+        <v>0.04857125505805016</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.00278912577778101</v>
+        <v>0.0162300206720829</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.003443355904892087</v>
+        <v>0.03309217840433121</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.006556133739650249</v>
+        <v>0.06733169406652451</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.01448271982371807</v>
+        <v>0.01276422385126352</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.003781444625928998</v>
+        <v>0.01893477514386177</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.001231531496159732</v>
+        <v>0.003712111385539174</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.0001364587515126914</v>
+        <v>0.001787693472579122</v>
       </c>
       <c r="B12" t="n">
-        <v>0.001865754253230989</v>
+        <v>0.03099801018834114</v>
       </c>
       <c r="C12" t="n">
-        <v>0.000145441445056349</v>
+        <v>0.005580267403274775</v>
       </c>
       <c r="D12" t="n">
-        <v>0.001105375355109572</v>
+        <v>0.03875160217285156</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0001262627338292077</v>
+        <v>0.003818864934146404</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0001354587002424523</v>
+        <v>0.02460803650319576</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0001974181941477582</v>
+        <v>0.01981895230710506</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0001927291159518063</v>
+        <v>0.02142170071601868</v>
       </c>
       <c r="I12" t="n">
-        <v>3.273557740612887e-05</v>
+        <v>0.003570763627067208</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0002694175345823169</v>
+        <v>0.0003850085195153952</v>
       </c>
       <c r="K12" t="n">
-        <v>0.001338033471256495</v>
+        <v>0.02414585649967194</v>
       </c>
       <c r="L12" t="n">
-        <v>5.76075108256191e-05</v>
+        <v>0.008741708472371101</v>
       </c>
       <c r="M12" t="n">
-        <v>0.001087121665477753</v>
+        <v>0.05454161018133163</v>
       </c>
       <c r="N12" t="n">
-        <v>0.000412977155065164</v>
+        <v>0.01911693438887596</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0004534655308816582</v>
+        <v>0.02543665282428265</v>
       </c>
       <c r="P12" t="n">
-        <v>6.327971641439945e-05</v>
+        <v>0.02012138441205025</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0001412962446920574</v>
+        <v>0.01173880975693464</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0001017556423903443</v>
+        <v>0.0009531143587082624</v>
       </c>
       <c r="S12" t="n">
-        <v>3.803497384069487e-05</v>
+        <v>0.0006609353586100042</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0003105405485257506</v>
+        <v>0.001109032775275409</v>
       </c>
       <c r="U12" t="n">
-        <v>7.118660141713917e-05</v>
+        <v>0.006109039299190044</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0001859660260379314</v>
+        <v>0.004487923346459866</v>
       </c>
       <c r="W12" t="n">
-        <v>2.613922333694063e-05</v>
+        <v>0.005977100227028131</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0001628112950129434</v>
+        <v>0.007506174966692924</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.0001755206612870097</v>
+        <v>0.001542732119560242</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.000109777320176363</v>
+        <v>0.004594538360834122</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.0001513436582172289</v>
+        <v>0.002457224763929844</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.0001513068855274469</v>
+        <v>0.003605432342737913</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.000373130984371528</v>
+        <v>0.0008186171762645245</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.846317824558355e-05</v>
+        <v>0.005759258754551411</v>
       </c>
       <c r="AE12" t="n">
-        <v>6.99791416991502e-06</v>
+        <v>0.004862484522163868</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.006502770906081e-05</v>
+        <v>0.005933581851422787</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.214282358181663e-05</v>
+        <v>0.0139574371278286</v>
       </c>
       <c r="AH12" t="n">
-        <v>8.616322884336114e-05</v>
+        <v>0.003498919773846865</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.526516618672758e-05</v>
+        <v>0.01089099422097206</v>
       </c>
       <c r="AJ12" t="n">
-        <v>5.044630597694777e-05</v>
+        <v>0.005867436528205872</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.0001042755829985254</v>
+        <v>0.00126732187345624</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.0001707993651507422</v>
+        <v>0.009928557090461254</v>
       </c>
       <c r="AM12" t="n">
-        <v>4.705621176981367e-05</v>
+        <v>0.008588576689362526</v>
       </c>
       <c r="AN12" t="n">
-        <v>5.589162174146622e-05</v>
+        <v>0.007514272816479206</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.0002052594063570723</v>
+        <v>0.002921485109254718</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.000205033618840389</v>
+        <v>0.009196585044264793</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8.431613969150931e-05</v>
+        <v>0.008348956704139709</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.0001182312480523251</v>
+        <v>0.001959519693627954</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.352078394731507e-05</v>
+        <v>0.003601140808314085</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.0001675998792052269</v>
+        <v>0.005218532402068377</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.001297095906920731</v>
+        <v>0.01324531249701977</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.21157991088694e-05</v>
+        <v>0.01345289126038551</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.0002306978567503393</v>
+        <v>0.01018316857516766</v>
       </c>
       <c r="AX12" t="n">
-        <v>2.82371329376474e-05</v>
+        <v>0.0314011238515377</v>
       </c>
       <c r="AY12" t="n">
-        <v>2.678508462850004e-05</v>
+        <v>0.0202360600233078</v>
       </c>
       <c r="AZ12" t="n">
-        <v>5.156314728083089e-06</v>
+        <v>0.002492789411917329</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.87168290419504e-06</v>
+        <v>0.001316524110734463</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.647510725888424e-05</v>
+        <v>0.003905616002157331</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.820828765630722e-05</v>
+        <v>0.0004541832022368908</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.00038484952528961</v>
+        <v>0.005282809026539326</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.0003110698889940977</v>
+        <v>0.003503066953271627</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.0002168818318750709</v>
+        <v>0.00804891437292099</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.0004653518262784928</v>
+        <v>0.01127880439162254</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.069368388736621e-05</v>
+        <v>0.002029740484431386</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.0001712135999696329</v>
+        <v>0.00590041745454073</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.0001733900426188484</v>
+        <v>0.01186305098235607</v>
       </c>
       <c r="BK12" t="n">
-        <v>9.895703260554001e-05</v>
+        <v>0.005587053950875998</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.0002356657350901514</v>
+        <v>0.002418221905827522</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.0003332699707243592</v>
+        <v>0.003123503644019365</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.0001994332706090063</v>
+        <v>0.0002432293258607388</v>
       </c>
       <c r="BO12" t="n">
-        <v>5.561247235164046e-05</v>
+        <v>0.0102734137326479</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.0001450743147870526</v>
+        <v>0.002184570301324129</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.0001300768344663084</v>
+        <v>0.0001089299912564456</v>
       </c>
       <c r="BR12" t="n">
-        <v>9.971528925234452e-06</v>
+        <v>0.001064109848812222</v>
       </c>
       <c r="BS12" t="n">
-        <v>2.074765507131815e-05</v>
+        <v>0.004103831481188536</v>
       </c>
       <c r="BT12" t="n">
-        <v>1.957564381882548e-05</v>
+        <v>0.003309832187369466</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.0001360020542051643</v>
+        <v>0.002039266983047128</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.0006630224524997175</v>
+        <v>0.01239139679819345</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.0001370534737361595</v>
+        <v>0.00760160107165575</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.0001978792570298538</v>
+        <v>0.01513173151761293</v>
       </c>
       <c r="BY12" t="n">
-        <v>9.112306725000963e-05</v>
+        <v>0.005029486026614904</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.0002040084073087201</v>
+        <v>0.01312594022601843</v>
       </c>
       <c r="CA12" t="n">
-        <v>8.608377538621426e-05</v>
+        <v>0.003365105018019676</v>
       </c>
       <c r="CB12" t="n">
-        <v>5.800973303848878e-05</v>
+        <v>0.0002465875586494803</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.0001422784698661417</v>
+        <v>0.002392102498561144</v>
       </c>
       <c r="CD12" t="n">
-        <v>8.961389539763331e-05</v>
+        <v>0.0001941080554388463</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.0003279167867731303</v>
+        <v>0.007345056161284447</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.0001029793347697705</v>
+        <v>0.001284185098484159</v>
       </c>
       <c r="CG12" t="n">
-        <v>9.561458136886358e-05</v>
+        <v>0.01341949217021465</v>
       </c>
       <c r="CH12" t="n">
-        <v>9.964517084881663e-05</v>
+        <v>0.0002414928021607921</v>
       </c>
       <c r="CI12" t="n">
-        <v>3.039193506992888e-05</v>
+        <v>0.004080647602677345</v>
       </c>
       <c r="CJ12" t="n">
-        <v>5.170339500182308e-05</v>
+        <v>0.001305093290284276</v>
       </c>
       <c r="CK12" t="n">
-        <v>2.633339317981154e-05</v>
+        <v>0.005784071981906891</v>
       </c>
       <c r="CL12" t="n">
-        <v>7.062982331262901e-05</v>
+        <v>0.002164421370252967</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.0003344447468407452</v>
+        <v>0.005407164804637432</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.0002254843420814723</v>
+        <v>0.0003827447071671486</v>
       </c>
       <c r="CO12" t="n">
-        <v>9.755069913808256e-05</v>
+        <v>0.01562492363154888</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.0003006513288710266</v>
+        <v>0.0203523151576519</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.0001597754890099168</v>
+        <v>0.005405365489423275</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.0002574499812908471</v>
+        <v>0.003468807321041822</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.0002219556190539151</v>
+        <v>0.008804578334093094</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.0003579966723918915</v>
+        <v>0.0059455088339746</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.614356369827874e-05</v>
+        <v>0.004958122503012419</v>
       </c>
       <c r="CV12" t="n">
-        <v>8.622433961136267e-05</v>
+        <v>0.000338864978402853</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.0002588570641819388</v>
+        <v>0.006438259966671467</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.0001438066392438486</v>
+        <v>0.002005113987252116</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.0001798033335944638</v>
+        <v>0.01425714325159788</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.0001199579928652383</v>
+        <v>0.004504913929849863</v>
       </c>
       <c r="DA12" t="n">
-        <v>5.112291546538472e-05</v>
+        <v>0.004658228252083063</v>
       </c>
       <c r="DB12" t="n">
-        <v>5.409253208199516e-05</v>
+        <v>0.0004026555398013443</v>
       </c>
       <c r="DC12" t="n">
-        <v>5.486935697263107e-05</v>
+        <v>0.005783651955425739</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.569090767996386e-05</v>
+        <v>0.002442277502268553</v>
       </c>
       <c r="DE12" t="n">
-        <v>7.34189961804077e-05</v>
+        <v>0.005790291354060173</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.0003515511925797909</v>
+        <v>0.007290144450962543</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.106486797652906e-05</v>
+        <v>0.00211297394707799</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.0004093438619747758</v>
+        <v>0.01345952227711678</v>
       </c>
       <c r="DI12" t="n">
-        <v>2.429160485917237e-05</v>
+        <v>0.0006783644785173237</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.0001654606749070808</v>
+        <v>0.02093224786221981</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.0002451551845297217</v>
+        <v>0.00243501178920269</v>
       </c>
       <c r="DL12" t="n">
-        <v>3.799901242018677e-05</v>
+        <v>0.02216493338346481</v>
       </c>
       <c r="DM12" t="n">
-        <v>3.404514245630708e-06</v>
+        <v>0.008346717804670334</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.0001616289519006386</v>
+        <v>0.0008684801869094372</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.0001237193500855938</v>
+        <v>0.006411067210137844</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.0001462964719394222</v>
+        <v>0.0001444851513952017</v>
       </c>
       <c r="DQ12" t="n">
-        <v>2.411390596535057e-06</v>
+        <v>0.004452700261026621</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.0002152089582523331</v>
+        <v>0.001577014802023768</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.0001718813582556322</v>
+        <v>0.004252484999597073</v>
       </c>
       <c r="DT12" t="n">
-        <v>1.776240242179483e-05</v>
+        <v>0.003457177663221955</v>
       </c>
       <c r="DU12" t="n">
-        <v>5.520828563021496e-05</v>
+        <v>0.009791966527700424</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.0001073733292287216</v>
+        <v>0.01267669815570116</v>
       </c>
       <c r="DW12" t="n">
-        <v>2.253496859339066e-06</v>
+        <v>0.0005110496422275901</v>
       </c>
       <c r="DX12" t="n">
-        <v>8.277693996205926e-05</v>
+        <v>0.004762417636811733</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.000165708435815759</v>
+        <v>0.01154179777950048</v>
       </c>
       <c r="DZ12" t="n">
-        <v>7.073904271237552e-06</v>
+        <v>0.005877404473721981</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.0001763877808116376</v>
+        <v>0.001503234729170799</v>
       </c>
       <c r="EB12" t="n">
-        <v>4.16386392316781e-05</v>
+        <v>0.006042130291461945</v>
       </c>
       <c r="EC12" t="n">
-        <v>7.509474380640313e-05</v>
+        <v>0.002353176008909941</v>
       </c>
       <c r="ED12" t="n">
-        <v>3.027373350050766e-05</v>
+        <v>0.01505126245319843</v>
       </c>
       <c r="EE12" t="n">
-        <v>4.502577576204203e-05</v>
+        <v>0.01187304779887199</v>
       </c>
       <c r="EF12" t="n">
-        <v>3.119360189884901e-05</v>
+        <v>0.004620948806405067</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.0001636224042158574</v>
+        <v>0.004276044201105833</v>
       </c>
       <c r="EH12" t="n">
-        <v>8.351550786755979e-05</v>
+        <v>0.005738143809139729</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.0001519388024462387</v>
+        <v>0.01349110156297684</v>
       </c>
       <c r="EJ12" t="n">
-        <v>8.830527804093435e-05</v>
+        <v>0.003655895590782166</v>
       </c>
       <c r="EK12" t="n">
-        <v>8.023757982300594e-05</v>
+        <v>0.002478624694049358</v>
       </c>
       <c r="EL12" t="n">
-        <v>5.330785643309355e-05</v>
+        <v>0.0005295464070513844</v>
       </c>
       <c r="EM12" t="n">
-        <v>2.252648664580192e-05</v>
+        <v>0.00213624001480639</v>
       </c>
       <c r="EN12" t="n">
-        <v>5.332201908458956e-05</v>
+        <v>0.0001886512618511915</v>
       </c>
       <c r="EO12" t="n">
-        <v>9.243839303962886e-05</v>
+        <v>0.0004172723274677992</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.0002254395512863994</v>
+        <v>0.008845014497637749</v>
       </c>
       <c r="EQ12" t="n">
-        <v>8.766756945988163e-05</v>
+        <v>0.001839659176766872</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.0001801307807909325</v>
+        <v>0.01246360316872597</v>
       </c>
       <c r="ES12" t="n">
-        <v>7.143837137846276e-05</v>
+        <v>0.00171016005333513</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.0001969804725376889</v>
+        <v>0.002059873659163713</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.000166013662237674</v>
+        <v>0.004309177864342928</v>
       </c>
       <c r="EV12" t="n">
-        <v>7.781656313454732e-05</v>
+        <v>0.006919628940522671</v>
       </c>
       <c r="EW12" t="n">
-        <v>1.043771590047982e-05</v>
+        <v>0.009999817237257957</v>
       </c>
       <c r="EX12" t="n">
-        <v>4.020534106530249e-05</v>
+        <v>0.0002322491782251745</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.000279072904959321</v>
+        <v>0.008328832685947418</v>
       </c>
       <c r="EZ12" t="n">
-        <v>8.987037290353328e-05</v>
+        <v>0.001305043464526534</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.0001592920598341152</v>
+        <v>0.01618331857025623</v>
       </c>
       <c r="FB12" t="n">
-        <v>8.268970850622281e-05</v>
+        <v>0.0009014724055305123</v>
       </c>
       <c r="FC12" t="n">
-        <v>7.6537617132999e-05</v>
+        <v>0.005006550811231136</v>
       </c>
       <c r="FD12" t="n">
-        <v>7.90790727478452e-05</v>
+        <v>0.0001904381206259131</v>
       </c>
       <c r="FE12" t="n">
-        <v>3.146641029161401e-05</v>
+        <v>0.005874580703675747</v>
       </c>
       <c r="FF12" t="n">
-        <v>6.881152512505651e-05</v>
+        <v>0.0005985625321045518</v>
       </c>
       <c r="FG12" t="n">
-        <v>1.683402297203429e-05</v>
+        <v>0.004653177224099636</v>
       </c>
       <c r="FH12" t="n">
-        <v>5.925063305767253e-05</v>
+        <v>0.005101339891552925</v>
       </c>
       <c r="FI12" t="n">
-        <v>9.151762787951156e-05</v>
+        <v>0.005166700109839439</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.0001619909889996052</v>
+        <v>0.005357909016311169</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.0001260850403923541</v>
+        <v>0.001099267159588635</v>
       </c>
       <c r="FL12" t="n">
-        <v>6.977248631301336e-06</v>
+        <v>0.002943073865026236</v>
       </c>
       <c r="FM12" t="n">
-        <v>6.818223482696339e-06</v>
+        <v>0.003346593584865332</v>
       </c>
       <c r="FN12" t="n">
-        <v>1.597652226337232e-05</v>
+        <v>0.006817284505814314</v>
       </c>
       <c r="FO12" t="n">
-        <v>3.917382855433971e-05</v>
+        <v>0.006119470112025738</v>
       </c>
       <c r="FP12" t="n">
-        <v>7.48959428165108e-05</v>
+        <v>0.005942424759268761</v>
       </c>
       <c r="FQ12" t="n">
-        <v>4.06361541536171e-05</v>
+        <v>0.01097615156322718</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.0001601609837962314</v>
+        <v>0.01144113391637802</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.0001028432307066396</v>
+        <v>0.00767548568546772</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.0001245719031430781</v>
+        <v>0.01619389094412327</v>
       </c>
       <c r="FU12" t="n">
-        <v>2.431628854537848e-05</v>
+        <v>0.006956761702895164</v>
       </c>
       <c r="FV12" t="n">
-        <v>8.031840843614191e-05</v>
+        <v>0.008287465199828148</v>
       </c>
       <c r="FW12" t="n">
-        <v>3.021060911123641e-05</v>
+        <v>0.02192570455372334</v>
       </c>
       <c r="FX12" t="n">
-        <v>3.973606726503931e-05</v>
+        <v>0.004016292747110128</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.0002368112473050132</v>
+        <v>0.003958404064178467</v>
       </c>
       <c r="FZ12" t="n">
-        <v>8.119820267893374e-05</v>
+        <v>0.001505772583186626</v>
       </c>
       <c r="GA12" t="n">
-        <v>1.295917354582343e-05</v>
+        <v>0.01041084714233875</v>
       </c>
       <c r="GB12" t="n">
-        <v>3.633671076386236e-05</v>
+        <v>0.01048154104501009</v>
       </c>
       <c r="GC12" t="n">
-        <v>2.90831576421624e-05</v>
+        <v>0.005073593463748693</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.0002539246925152838</v>
+        <v>0.0130821131169796</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.0004399201134219766</v>
+        <v>0.006970169022679329</v>
       </c>
       <c r="GF12" t="n">
-        <v>7.264243322424591e-05</v>
+        <v>0.003726722206920385</v>
       </c>
       <c r="GG12" t="n">
-        <v>4.369523958303034e-05</v>
+        <v>0.001076048240065575</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.00166936544701457</v>
+        <v>0.006830494850873947</v>
       </c>
       <c r="B13" t="n">
-        <v>0.003448622999712825</v>
+        <v>0.1035937368869781</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0002234987914562225</v>
+        <v>0.01456469856202602</v>
       </c>
       <c r="D13" t="n">
-        <v>0.002777663758024573</v>
+        <v>0.02699562162160873</v>
       </c>
       <c r="E13" t="n">
-        <v>0.004517583642154932</v>
+        <v>0.05961887165904045</v>
       </c>
       <c r="F13" t="n">
-        <v>0.008340464904904366</v>
+        <v>0.1010062098503113</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0006180091295391321</v>
+        <v>0.01781017705798149</v>
       </c>
       <c r="H13" t="n">
-        <v>0.005227227229624987</v>
+        <v>0.07023686915636063</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0005305028171278536</v>
+        <v>0.03695337846875191</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0001937196357175708</v>
+        <v>0.02462398074567318</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00378958904184401</v>
+        <v>0.1557163894176483</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0009165004594251513</v>
+        <v>0.001441788859665394</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0009659926290623844</v>
+        <v>0.06758218258619308</v>
       </c>
       <c r="N13" t="n">
-        <v>0.002227198099717498</v>
+        <v>0.04196557030081749</v>
       </c>
       <c r="O13" t="n">
-        <v>0.006999117787927389</v>
+        <v>0.110668882727623</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0007546728011220694</v>
+        <v>0.05511616170406342</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.004463383927941322</v>
+        <v>0.00080909114331007</v>
       </c>
       <c r="R13" t="n">
-        <v>0.000207785444217734</v>
+        <v>0.02998378500342369</v>
       </c>
       <c r="S13" t="n">
-        <v>0.000596697733271867</v>
+        <v>0.01710820943117142</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0001468859554734081</v>
+        <v>0.03293321281671524</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0001178956881631166</v>
+        <v>0.01839666068553925</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0005748908151872456</v>
+        <v>0.07169169932603836</v>
       </c>
       <c r="W13" t="n">
-        <v>0.003251881804317236</v>
+        <v>0.07338747382164001</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0009418085683137178</v>
+        <v>0.02470434084534645</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.000780382426455617</v>
+        <v>0.01187149994075298</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.0006763947894796729</v>
+        <v>0.01729522459208965</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.0001151814358308911</v>
+        <v>0.0139653068035841</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.621400386095047e-05</v>
+        <v>0.006681849714368582</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.0004817339940927923</v>
+        <v>0.03753581643104553</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.64262780547142e-08</v>
+        <v>0.01503663044422865</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.0003419571148697287</v>
+        <v>0.07530200481414795</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0007095619803294539</v>
+        <v>0.0927204042673111</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.0003108272212557495</v>
+        <v>0.06695490330457687</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.0007041072240099311</v>
+        <v>0.01606985926628113</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.001551310415379703</v>
+        <v>0.03588894754648209</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0005052872584201396</v>
+        <v>0.01463575474917889</v>
       </c>
       <c r="AK13" t="n">
-        <v>8.175754192052409e-05</v>
+        <v>0.004752670414745808</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.0005275230505503714</v>
+        <v>0.04219210520386696</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.0003479438310023397</v>
+        <v>0.006734917871654034</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.0003935896675102413</v>
+        <v>0.03864281624555588</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.0001908093690872192</v>
+        <v>0.02298434637486935</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.0004589313757605851</v>
+        <v>0.02594881504774094</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.0001228091132361442</v>
+        <v>0.03705143183469772</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.001182801672257483</v>
+        <v>0.06154696270823479</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.091026393231004e-05</v>
+        <v>0.02073689550161362</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.0006443242309615016</v>
+        <v>0.02910641208291054</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.0005804577376693487</v>
+        <v>0.2753393948078156</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.0003836178511846811</v>
+        <v>0.005648152437061071</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.002977886702865362</v>
+        <v>0.05041379854083061</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.004031086340546608</v>
+        <v>0.01303409691900015</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.005241080652922392</v>
+        <v>0.06117194518446922</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.0009443456074222922</v>
+        <v>0.02432198636233807</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.0002549692871980369</v>
+        <v>0.02760016918182373</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.0003241233644075692</v>
+        <v>0.01008977927267551</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.001318984432145953</v>
+        <v>0.04794741421937943</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.001496266690082848</v>
+        <v>0.06967060267925262</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.0008164495229721069</v>
+        <v>0.01131766382604837</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.001746432157233357</v>
+        <v>0.01618640124797821</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.000394680944737047</v>
+        <v>0.01818888261914253</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.001628702157177031</v>
+        <v>0.03287126123905182</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.0004401213373057544</v>
+        <v>0.06684111058712006</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.001889249193482101</v>
+        <v>0.02035794965922832</v>
       </c>
       <c r="BK13" t="n">
-        <v>9.912363020703197e-05</v>
+        <v>0.023509556427598</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.0002540240529924631</v>
+        <v>0.03249335661530495</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.0002630912349559367</v>
+        <v>0.02497494034469128</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.0002345931134186685</v>
+        <v>0.01220410503447056</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.002428828971460462</v>
+        <v>0.03537065908312798</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.0008733088034205139</v>
+        <v>0.001909483456984162</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.0002204658230766654</v>
+        <v>0.002827792661264539</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.0002562159788794816</v>
+        <v>0.07774150371551514</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.001660537673160434</v>
+        <v>0.04154017567634583</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.0002305007656104863</v>
+        <v>0.006952953059226274</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.076095577445813e-05</v>
+        <v>0.03546057641506195</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.001087194308638573</v>
+        <v>0.1288004517555237</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.0002377987839281559</v>
+        <v>0.02188955061137676</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.002021994907408953</v>
+        <v>0.07462635636329651</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.002152985893189907</v>
+        <v>0.03228353708982468</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.004073359537869692</v>
+        <v>0.07976602017879486</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.0008630098309367895</v>
+        <v>0.01225415710359812</v>
       </c>
       <c r="CB13" t="n">
-        <v>1.224322477355599e-05</v>
+        <v>0.005060285795480013</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.0004596014332491904</v>
+        <v>0.02440273389220238</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.000211709615541622</v>
+        <v>0.01560963224619627</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.000184443561010994</v>
+        <v>0.03639157488942146</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.0002489067264832556</v>
+        <v>0.01036450266838074</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.0002031761541729793</v>
+        <v>0.01517128199338913</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.001091316808015108</v>
+        <v>0.009788341820240021</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.001451210118830204</v>
+        <v>0.02913288027048111</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.0005986221367493272</v>
+        <v>0.01890031062066555</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.0009320423705503345</v>
+        <v>0.02556602656841278</v>
       </c>
       <c r="CL13" t="n">
-        <v>7.599673699587584e-05</v>
+        <v>0.01171926595270634</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.0001749501097947359</v>
+        <v>0.05072785168886185</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.001251952489838004</v>
+        <v>0.1385441422462463</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.0006014413083903491</v>
+        <v>0.004195126239210367</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.001805484527722001</v>
+        <v>0.007636669091880322</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.001733499113470316</v>
+        <v>0.07497929036617279</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.00140467332676053</v>
+        <v>0.05323723703622818</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.001394472550600767</v>
+        <v>0.02578158676624298</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.002020144602283835</v>
+        <v>0.03130175545811653</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.000127185630844906</v>
+        <v>0.03539685904979706</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.0002444051788188517</v>
+        <v>0.02676842547953129</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.0002263838250655681</v>
+        <v>0.03326473757624626</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.0002082940191030502</v>
+        <v>0.005614136345684528</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.0001398261083522812</v>
+        <v>0.01011186093091965</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.000860776228364557</v>
+        <v>0.01958275400102139</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.001542074256576598</v>
+        <v>0.0225639995187521</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.0002233120030723512</v>
+        <v>0.01109618227928877</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.0007364435587078333</v>
+        <v>0.02141489088535309</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.0004155245260335505</v>
+        <v>0.01393626444041729</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.001956939464434981</v>
+        <v>0.02684430591762066</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.0007024699007160962</v>
+        <v>0.0136690242215991</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.00027814696659334</v>
+        <v>0.02673760801553726</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.004225924611091614</v>
+        <v>0.04227878525853157</v>
       </c>
       <c r="DI13" t="n">
-        <v>8.05772069725208e-05</v>
+        <v>0.05487185716629028</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.0008856805507093668</v>
+        <v>0.01146769244223833</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.001531093847006559</v>
+        <v>0.006759378127753735</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.0008705609943717718</v>
+        <v>0.02894280292093754</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.001269074622541666</v>
+        <v>0.02733015082776546</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.001286087208427489</v>
+        <v>0.009786834940314293</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.0009358077077195048</v>
+        <v>0.01662655547261238</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.0002094926167046651</v>
+        <v>0.0005854747723788023</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.0001453171717002988</v>
+        <v>0.07951608300209045</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.001379663590341806</v>
+        <v>0.02928756363689899</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.001910048769786954</v>
+        <v>0.04130218178033829</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.001652079401537776</v>
+        <v>0.0008153091184794903</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.0006727491854690015</v>
+        <v>0.0126986326649785</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.0004665410087909549</v>
+        <v>0.02643660083413124</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.0001741344749461859</v>
+        <v>0.0008665770292282104</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.001245598425157368</v>
+        <v>0.01868971437215805</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.0006232403102330863</v>
+        <v>0.006402309983968735</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.0008578742854297161</v>
+        <v>0.02396865375339985</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.00125500001013279</v>
+        <v>0.001598917762748897</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.0006941173924133182</v>
+        <v>0.02946246787905693</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.0005476030637510121</v>
+        <v>0.01843789964914322</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.0004599520179908723</v>
+        <v>0.01529739424586296</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.0008954136283136904</v>
+        <v>0.0353333055973053</v>
       </c>
       <c r="EF13" t="n">
-        <v>3.042425669264048e-05</v>
+        <v>0.01205265056341887</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.0009512999095022678</v>
+        <v>0.004781567491590977</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.0005947562167420983</v>
+        <v>0.01271176524460316</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.001173043623566628</v>
+        <v>0.04505101218819618</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.0007992595783434808</v>
+        <v>0.02929829433560371</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.001169595052488148</v>
+        <v>0.001849786378443241</v>
       </c>
       <c r="EL13" t="n">
-        <v>9.930069791153073e-05</v>
+        <v>0.01175370998680592</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.0006518409354612231</v>
+        <v>0.01097641605883837</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.0003648321435321122</v>
+        <v>0.01328974962234497</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.0007685237214900553</v>
+        <v>0.02320990525186062</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.0001939723151735961</v>
+        <v>0.008745625615119934</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.0002241400652565062</v>
+        <v>0.03411021083593369</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.0009872543159872293</v>
+        <v>0.009087191894650459</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.0009464985923841596</v>
+        <v>0.008239349350333214</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.0001265459140995517</v>
+        <v>0.01672069169580936</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.0001945242984220386</v>
+        <v>0.02634964697062969</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.003576743183657527</v>
+        <v>0.03186075761914253</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.0009626925457268953</v>
+        <v>0.01640407927334309</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.0004262049333192408</v>
+        <v>0.02448292262852192</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.0002962621801998466</v>
+        <v>0.04379206150770187</v>
       </c>
       <c r="EZ13" t="n">
-        <v>8.92754178494215e-05</v>
+        <v>0.01606375724077225</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.0002234926214441657</v>
+        <v>0.01391648221760988</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.001247681910172105</v>
+        <v>0.01666942238807678</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.001335164648480713</v>
+        <v>0.02758234180510044</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.0005713134887628257</v>
+        <v>0.02152771502733231</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.000999681418761611</v>
+        <v>0.02542377077043056</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.0002566493058111519</v>
+        <v>0.01656264066696167</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.0008524016593582928</v>
+        <v>0.03584938123822212</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.0001483247033320367</v>
+        <v>0.06399376690387726</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.0001327979261986911</v>
+        <v>0.007382375188171864</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.002632993273437023</v>
+        <v>0.03532453626394272</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.001143912319093943</v>
+        <v>0.02218417078256607</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.0004711351648438722</v>
+        <v>0.03501670435070992</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.0001643685100134462</v>
+        <v>0.03591050207614899</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.0004897695034742355</v>
+        <v>0.03427794203162193</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.0004189182945992798</v>
+        <v>0.005359833594411612</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.0006730311433784664</v>
+        <v>0.02755318582057953</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.002820095047354698</v>
+        <v>0.116415299475193</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.0004763867182191461</v>
+        <v>0.03015385940670967</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.0005987031618133187</v>
+        <v>0.009042274206876755</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.004430990200489759</v>
+        <v>0.01530239544808865</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.000687493709847331</v>
+        <v>0.005750877782702446</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.0007388237281702459</v>
+        <v>0.03031410649418831</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.003295687958598137</v>
+        <v>0.01636944897472858</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.001357809407636523</v>
+        <v>0.02716527134180069</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.0008722780621610582</v>
+        <v>0.003207148751243949</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.001317010377533734</v>
+        <v>0.008107183501124382</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.0002625164052005857</v>
+        <v>0.02131210267543793</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.0005818323697894812</v>
+        <v>0.03086607530713081</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.002034298842772841</v>
+        <v>0.009137570858001709</v>
       </c>
       <c r="GD13" t="n">
-        <v>5.807616980746388e-05</v>
+        <v>0.002831018529832363</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.001701054745353758</v>
+        <v>0.0159875825047493</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.0007453833241015673</v>
+        <v>0.02241825684905052</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.0001701003056950867</v>
+        <v>0.02280987799167633</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.01050173491239548</v>
+        <v>0.05821770057082176</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0007564560510218143</v>
+        <v>0.01292035169899464</v>
       </c>
       <c r="C14" t="n">
-        <v>0.002514334861189127</v>
+        <v>0.02719220705330372</v>
       </c>
       <c r="D14" t="n">
-        <v>0.006291531026363373</v>
+        <v>0.1585304290056229</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001747955684550107</v>
+        <v>0.05856043100357056</v>
       </c>
       <c r="F14" t="n">
-        <v>0.002598877297714353</v>
+        <v>0.03389575332403183</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001549510518088937</v>
+        <v>0.07532310485839844</v>
       </c>
       <c r="H14" t="n">
-        <v>0.001066891360096633</v>
+        <v>0.0104479705914855</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0003503976913634688</v>
+        <v>0.02182642929255962</v>
       </c>
       <c r="J14" t="n">
-        <v>0.009214379824697971</v>
+        <v>0.02188721671700478</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0008370316354557872</v>
+        <v>0.04373028501868248</v>
       </c>
       <c r="L14" t="n">
-        <v>0.003069570288062096</v>
+        <v>0.04260651767253876</v>
       </c>
       <c r="M14" t="n">
-        <v>0.002464102115482092</v>
+        <v>0.2151909023523331</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0023857899941504</v>
+        <v>0.008412085473537445</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0004881910281255841</v>
+        <v>0.03459146618843079</v>
       </c>
       <c r="P14" t="n">
-        <v>0.000277721497695893</v>
+        <v>0.05044511333107948</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0012892090016976</v>
+        <v>0.05177867412567139</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0007166711729951203</v>
+        <v>0.01976031623780727</v>
       </c>
       <c r="S14" t="n">
-        <v>0.001464126631617546</v>
+        <v>0.0006048749200999737</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0022189577575773</v>
+        <v>0.003868402913212776</v>
       </c>
       <c r="U14" t="n">
-        <v>0.001025112578645349</v>
+        <v>0.003750865114852786</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0001962576352525502</v>
+        <v>0.01648003235459328</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0009395908564329147</v>
+        <v>0.01894580759108067</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0003293401678092778</v>
+        <v>0.07668088376522064</v>
       </c>
       <c r="Y14" t="n">
-        <v>9.469993528909981e-05</v>
+        <v>0.00758830551058054</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.001664177631027997</v>
+        <v>0.0005954992957413197</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0003784531727433205</v>
+        <v>0.003914563450962305</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.001051105558872223</v>
+        <v>0.0123234186321497</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.002359914127737284</v>
+        <v>0.007431014440953732</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0006234904285520315</v>
+        <v>0.005363437347114086</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.0005378745263442397</v>
+        <v>0.02044666185975075</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.001049193437211215</v>
+        <v>0.08616778254508972</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.0007288622437044978</v>
+        <v>0.05819376558065414</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.0004736215341836214</v>
+        <v>0.03259087726473808</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.0008894946076907218</v>
+        <v>0.0413176454603672</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.0006562877679243684</v>
+        <v>0.04318778961896896</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.001467940048314631</v>
+        <v>0.008667053654789925</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.080065991729498e-05</v>
+        <v>0.01987921074032784</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.0004609531897585839</v>
+        <v>0.03093722648918629</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.001056008390150964</v>
+        <v>0.0463312566280365</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.001367094460874796</v>
+        <v>0.02876627817749977</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.0005880944081582129</v>
+        <v>0.02241835370659828</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.001289719948545098</v>
+        <v>0.05262208357453346</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.001265030237846076</v>
+        <v>0.02053850702941418</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.0005803233361802995</v>
+        <v>0.0008759542251937091</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.006621968001127243</v>
+        <v>0.02152683399617672</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.002152825240045786</v>
+        <v>0.00502723827958107</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.002807668410241604</v>
+        <v>0.009328450076282024</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.003620513714849949</v>
+        <v>0.1047991067171097</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.002346037654206157</v>
+        <v>0.01956672221422195</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.0005687958328053355</v>
+        <v>0.03266074135899544</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.0005854620831087232</v>
+        <v>0.03452387824654579</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.002310347277671099</v>
+        <v>0.01901428401470184</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.0009105396457016468</v>
+        <v>0.03353453800082207</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.004249491728842258</v>
+        <v>0.06224073469638824</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.005419149063527584</v>
+        <v>0.006706104148179293</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.0004468848346732557</v>
+        <v>0.004603015724569559</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.0004702541045844555</v>
+        <v>0.05980083346366882</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.001683171256445348</v>
+        <v>0.08877326548099518</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.659108425490558e-05</v>
+        <v>0.02417834848165512</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.0005397822242230177</v>
+        <v>0.06254231184720993</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.002560549648478627</v>
+        <v>0.007800305727869272</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.001679806970059872</v>
+        <v>0.06108075752854347</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.0005769968265667558</v>
+        <v>0.0004808660596609116</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.002488788682967424</v>
+        <v>0.03274263441562653</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.0004808885860256851</v>
+        <v>0.02294383198022842</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.0005625608027912676</v>
+        <v>0.01847446523606777</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.0005804807879030704</v>
+        <v>0.03268834948539734</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.0009372135391458869</v>
+        <v>0.005205401219427586</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.001105583622120321</v>
+        <v>0.0002542457077652216</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.0004598313244059682</v>
+        <v>0.00534520111978054</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.0008401621598750353</v>
+        <v>0.01110157091170549</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.002869532443583012</v>
+        <v>0.00977653544396162</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.0001035601308103651</v>
+        <v>0.03352979943156242</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.001123433234170079</v>
+        <v>0.002397247590124607</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.001537587959319353</v>
+        <v>0.1058908551931381</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.0002346262917853892</v>
+        <v>0.02746975421905518</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.0003938801819458604</v>
+        <v>0.04133550450205803</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.0005229492671787739</v>
+        <v>0.01850795745849609</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.001637814682908356</v>
+        <v>0.01444102823734283</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.0004193983040750027</v>
+        <v>0.02701673842966557</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.002023672219365835</v>
+        <v>0.01338578388094902</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.001502062194049358</v>
+        <v>0.003738071769475937</v>
       </c>
       <c r="CF14" t="n">
-        <v>5.420617526397109e-06</v>
+        <v>0.007007105275988579</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.0005768678965978324</v>
+        <v>0.05283096432685852</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.0001066087206709199</v>
+        <v>0.01032963860780001</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.001405467046424747</v>
+        <v>0.0227360725402832</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.576404949650168e-05</v>
+        <v>0.001627112505957484</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.001214729738421738</v>
+        <v>0.01155365444719791</v>
       </c>
       <c r="CL14" t="n">
-        <v>0.0002063660213025287</v>
+        <v>0.01424742117524147</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.002516514156013727</v>
+        <v>0.01485868915915489</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.000830874138046056</v>
+        <v>0.0292494036257267</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.0001003705838229507</v>
+        <v>0.02533983439207077</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.002274278784170747</v>
+        <v>0.05893482267856598</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.003113775048404932</v>
+        <v>0.0794798880815506</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.0007869007531553507</v>
+        <v>0.0141779612749815</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.002240808680653572</v>
+        <v>0.02323123067617416</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.003861335106194019</v>
+        <v>0.01099754963070154</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.0009505163179710507</v>
+        <v>0.07610529661178589</v>
       </c>
       <c r="CV14" t="n">
-        <v>0.001506694359704852</v>
+        <v>0.01390649192035198</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.00176537421066314</v>
+        <v>0.002709319349378347</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.0001734806864988059</v>
+        <v>0.004966817796230316</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.0007190221804194152</v>
+        <v>0.05390411987900734</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.0001112302634282969</v>
+        <v>0.008344340138137341</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.00106937694363296</v>
+        <v>0.02351103723049164</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.0001792673720046878</v>
+        <v>0.004412560723721981</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.0009158776374533772</v>
+        <v>0.00967030506581068</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.000179326074430719</v>
+        <v>0.006022418383508921</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.001201523235067725</v>
+        <v>0.01618528366088867</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.002134585753083229</v>
+        <v>0.02418613247573376</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.002912910189479589</v>
+        <v>0.01544284820556641</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.00364292087033391</v>
+        <v>0.0533289797604084</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.0005140498396940529</v>
+        <v>0.01296501886099577</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.0006665245746262372</v>
+        <v>0.005319499410688877</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.001025411416776478</v>
+        <v>0.02749679237604141</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.004379014018923044</v>
+        <v>0.1185853555798531</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.0008872740436345339</v>
+        <v>0.02118377387523651</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.0009116295841522515</v>
+        <v>0.02029574289917946</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.0002309531555511057</v>
+        <v>0.01761962845921516</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.0007855809526517987</v>
+        <v>0.03484310954809189</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.0009535087738186121</v>
+        <v>0.005863189697265625</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.00235738349147141</v>
+        <v>0.01057039760053158</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.0008419759687967598</v>
+        <v>0.01595141738653183</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.0008136490359902382</v>
+        <v>0.008118324913084507</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.0003393536317162216</v>
+        <v>0.00986192375421524</v>
       </c>
       <c r="DV14" t="n">
-        <v>0.001362241921015084</v>
+        <v>0.07821699976921082</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.00203878921456635</v>
+        <v>0.01427276711910963</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.001487813657149673</v>
+        <v>0.00299902493134141</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.000370398658560589</v>
+        <v>0.04673361778259277</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.0009201281936839223</v>
+        <v>0.00471828505396843</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.001044851611368358</v>
+        <v>0.01449251268059015</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.0006370110204443336</v>
+        <v>0.007002671714872122</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.0003040885785594583</v>
+        <v>0.009626977145671844</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.0001836243900470436</v>
+        <v>0.06835091859102249</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.0006637233309447765</v>
+        <v>0.05144289135932922</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.0019664925057441</v>
+        <v>0.02199330367147923</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.002301768166944385</v>
+        <v>0.01040357816964388</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.001227330649271607</v>
+        <v>0.006680313032120466</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.00244476180523634</v>
+        <v>0.06382187455892563</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.002473931992426515</v>
+        <v>0.005821263417601585</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.0005324967205524445</v>
+        <v>0.01106972806155682</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.0001218881370732561</v>
+        <v>0.008386525325477123</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.0002504348813090473</v>
+        <v>0.01156210340559483</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.0002731033600866795</v>
+        <v>0.01962954364717007</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.0001233993680216372</v>
+        <v>0.001024647615849972</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.003386748488992453</v>
+        <v>0.006325792521238327</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.0007054522284306586</v>
+        <v>0.002023342996835709</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.0001350081292912364</v>
+        <v>0.07300590723752975</v>
       </c>
       <c r="ES14" t="n">
-        <v>9.860075078904629e-05</v>
+        <v>0.01368826627731323</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.001453239237889647</v>
+        <v>0.0573403611779213</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.0009384283912368119</v>
+        <v>0.02382337860763073</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.0004458822368178517</v>
+        <v>0.002472091466188431</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.00206280592828989</v>
+        <v>0.02926101535558701</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.001645014039240777</v>
+        <v>0.0139476777985692</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.001769150258041918</v>
+        <v>0.001865445170551538</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.0003448915667831898</v>
+        <v>0.007271669339388609</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.0006347264861688018</v>
+        <v>0.06517188251018524</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.0001528508437331766</v>
+        <v>0.01229891926050186</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.001107720891013741</v>
+        <v>0.002295392565429211</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.0002022648986894637</v>
+        <v>0.00531322043389082</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.001024747616611421</v>
+        <v>0.01489893533289433</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.0002846250717993826</v>
+        <v>0.0003889775834977627</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.0002588019124232233</v>
+        <v>0.0006351761985570192</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.002448909683153033</v>
+        <v>0.007499315775930882</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.002487952820956707</v>
+        <v>0.01297508366405964</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.0004698792472481728</v>
+        <v>0.02172963693737984</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.0009604080696590245</v>
+        <v>0.03414147719740868</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.00254782335832715</v>
+        <v>0.006871504709124565</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.001312646549195051</v>
+        <v>0.02852293290197849</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.0006549263489432633</v>
+        <v>0.01693727448582649</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.0008791880682110786</v>
+        <v>0.03251650929450989</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.001450680661946535</v>
+        <v>0.002283507026731968</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.001101318397559226</v>
+        <v>0.02885962463915348</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.001704101450741291</v>
+        <v>0.01721134409308434</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.001851035747677088</v>
+        <v>0.05193591490387917</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.002833271631971002</v>
+        <v>0.0784701481461525</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.002354091266170144</v>
+        <v>0.03282900527119637</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.001280519179999828</v>
+        <v>0.02463512308895588</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.0003927809884771705</v>
+        <v>0.02411013841629028</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.0005421803798526525</v>
+        <v>0.01692091673612595</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.00100234616547823</v>
+        <v>0.0007491549476981163</v>
       </c>
       <c r="FZ14" t="n">
-        <v>1.22649798868224e-05</v>
+        <v>0.01803221367299557</v>
       </c>
       <c r="GA14" t="n">
-        <v>5.170120857656002e-06</v>
+        <v>0.006909850519150496</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.0001564878039062023</v>
+        <v>0.07925520092248917</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.001227733679115772</v>
+        <v>0.03233537822961807</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.0002073278010357171</v>
+        <v>0.02689663507044315</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.0009955022251233459</v>
+        <v>0.05445998907089233</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.0004263925948180258</v>
+        <v>0.004223959986120462</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.001087187556549907</v>
+        <v>0.01241973601281643</v>
       </c>
     </row>
     <row r="15">
@@ -9534,571 +9534,571 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2.934546827759732e-09</v>
+        <v>8.363091469343331e-11</v>
       </c>
       <c r="B17" t="n">
-        <v>2.484724603846189e-08</v>
+        <v>2.520209041456667e-10</v>
       </c>
       <c r="C17" t="n">
-        <v>3.654305080758036e-09</v>
+        <v>4.449280874285755e-11</v>
       </c>
       <c r="D17" t="n">
-        <v>4.965550459701262e-08</v>
+        <v>3.795259106986748e-10</v>
       </c>
       <c r="E17" t="n">
-        <v>9.318380733702725e-09</v>
+        <v>2.787412245464083e-10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.053773411920702e-08</v>
+        <v>2.786281483313502e-10</v>
       </c>
       <c r="G17" t="n">
-        <v>1.115397640916171e-08</v>
+        <v>2.420330880159582e-10</v>
       </c>
       <c r="H17" t="n">
-        <v>2.112722441438564e-08</v>
+        <v>4.036358469683421e-10</v>
       </c>
       <c r="I17" t="n">
-        <v>1.477547506567589e-08</v>
+        <v>2.514741193060388e-10</v>
       </c>
       <c r="J17" t="n">
-        <v>2.179082470021854e-09</v>
+        <v>2.800653459145153e-11</v>
       </c>
       <c r="K17" t="n">
-        <v>2.177339375464271e-08</v>
+        <v>1.494186718797863e-10</v>
       </c>
       <c r="L17" t="n">
-        <v>3.351003474705294e-09</v>
+        <v>2.828499240381532e-11</v>
       </c>
       <c r="M17" t="n">
-        <v>2.855500369491892e-08</v>
+        <v>5.71677816196825e-10</v>
       </c>
       <c r="N17" t="n">
-        <v>1.745809186104452e-08</v>
+        <v>4.652478124977932e-10</v>
       </c>
       <c r="O17" t="n">
-        <v>1.144837202815552e-08</v>
+        <v>2.8606669810749e-10</v>
       </c>
       <c r="P17" t="n">
-        <v>3.871361453633426e-09</v>
+        <v>2.771199936191238e-10</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.294340634672153e-09</v>
+        <v>3.811000681697152e-10</v>
       </c>
       <c r="R17" t="n">
-        <v>3.312181640069412e-10</v>
+        <v>2.325250547663416e-10</v>
       </c>
       <c r="S17" t="n">
-        <v>5.793754920269123e-10</v>
+        <v>2.608440199947104e-11</v>
       </c>
       <c r="T17" t="n">
-        <v>1.122864823344116e-08</v>
+        <v>1.041719072114589e-10</v>
       </c>
       <c r="U17" t="n">
-        <v>9.890246399635316e-10</v>
+        <v>1.489737638804556e-10</v>
       </c>
       <c r="V17" t="n">
-        <v>3.717997021368546e-09</v>
+        <v>4.602190503688597e-11</v>
       </c>
       <c r="W17" t="n">
-        <v>1.794469639548879e-08</v>
+        <v>1.035811089677985e-10</v>
       </c>
       <c r="X17" t="n">
-        <v>7.41405425941366e-09</v>
+        <v>1.00753060408576e-11</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.15265121891639e-08</v>
+        <v>6.726926654598842e-11</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.505144536257831e-09</v>
+        <v>9.459970307101884e-11</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.326298981751961e-08</v>
+        <v>6.384800674275048e-12</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.521651071811903e-08</v>
+        <v>1.39638049387325e-11</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.07661603468523e-08</v>
+        <v>1.287492890078568e-10</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.257094606188502e-08</v>
+        <v>2.41997359651247e-11</v>
       </c>
       <c r="AE17" t="n">
-        <v>9.948091239664336e-10</v>
+        <v>1.161399448834644e-10</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.720969922125448e-09</v>
+        <v>8.266887174812609e-11</v>
       </c>
       <c r="AG17" t="n">
-        <v>6.890274573123634e-09</v>
+        <v>1.044617864431885e-10</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.310488872974247e-08</v>
+        <v>8.632091569316103e-11</v>
       </c>
       <c r="AI17" t="n">
-        <v>5.706243033642977e-09</v>
+        <v>1.868440541175076e-10</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.381240316040589e-09</v>
+        <v>4.768438074953529e-11</v>
       </c>
       <c r="AK17" t="n">
-        <v>7.378169630811726e-09</v>
+        <v>9.947695445156057e-12</v>
       </c>
       <c r="AL17" t="n">
-        <v>6.972078914202484e-09</v>
+        <v>7.210047142658382e-11</v>
       </c>
       <c r="AM17" t="n">
-        <v>3.796994718641145e-09</v>
+        <v>1.881948208382056e-10</v>
       </c>
       <c r="AN17" t="n">
-        <v>3.172131668449651e-09</v>
+        <v>1.168471014389993e-10</v>
       </c>
       <c r="AO17" t="n">
-        <v>9.010433510425742e-10</v>
+        <v>8.951497182385637e-11</v>
       </c>
       <c r="AP17" t="n">
-        <v>5.244665146619809e-09</v>
+        <v>1.241470988511129e-11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.189673870527486e-08</v>
+        <v>3.585760161017859e-11</v>
       </c>
       <c r="AR17" t="n">
-        <v>7.784819899825379e-09</v>
+        <v>5.130396454888775e-11</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.392722020516658e-09</v>
+        <v>3.466747722224994e-11</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.783443253662199e-09</v>
+        <v>2.248231184553973e-10</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.887214828855122e-08</v>
+        <v>2.552948408229838e-10</v>
       </c>
       <c r="AV17" t="n">
-        <v>6.943337016451778e-09</v>
+        <v>1.984786779374303e-10</v>
       </c>
       <c r="AW17" t="n">
-        <v>6.194813551019251e-09</v>
+        <v>6.82124218220892e-11</v>
       </c>
       <c r="AX17" t="n">
-        <v>4.085078053606139e-09</v>
+        <v>4.511858109346178e-10</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.124437876143247e-09</v>
+        <v>2.815337685202479e-10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3.360300482313505e-09</v>
+        <v>9.192147043535215e-11</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.751110781522129e-09</v>
+        <v>5.852515694293459e-11</v>
       </c>
       <c r="BB17" t="n">
-        <v>2.373732099769654e-09</v>
+        <v>6.039267003155047e-11</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.325830911724779e-08</v>
+        <v>5.465033980911471e-11</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.368589046066518e-09</v>
+        <v>1.827002438226089e-10</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.334307383644045e-09</v>
+        <v>7.828215159433327e-11</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.510501471268526e-09</v>
+        <v>1.979548330810488e-10</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.818901829153674e-08</v>
+        <v>2.531136689132296e-10</v>
       </c>
       <c r="BH17" t="n">
-        <v>1.889418754785765e-08</v>
+        <v>1.064463031608121e-10</v>
       </c>
       <c r="BI17" t="n">
-        <v>6.769102611769995e-09</v>
+        <v>2.564778597835549e-11</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1.463218168851199e-08</v>
+        <v>2.182254515981086e-10</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.17794929366255e-09</v>
+        <v>1.224800955101912e-10</v>
       </c>
       <c r="BL17" t="n">
-        <v>7.117919587074084e-09</v>
+        <v>5.524082233310246e-11</v>
       </c>
       <c r="BM17" t="n">
-        <v>9.450815241507371e-09</v>
+        <v>2.427383571923514e-10</v>
       </c>
       <c r="BN17" t="n">
-        <v>3.462522935038237e-09</v>
+        <v>7.909941451833546e-11</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.053561504704703e-08</v>
+        <v>1.476699179603358e-10</v>
       </c>
       <c r="BP17" t="n">
-        <v>1.06641779851202e-08</v>
+        <v>2.096796625217223e-10</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.709283381501336e-09</v>
+        <v>1.426918218999651e-11</v>
       </c>
       <c r="BR17" t="n">
-        <v>7.644210597845813e-09</v>
+        <v>7.580269745233181e-11</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.367775936955695e-08</v>
+        <v>6.473824254449312e-11</v>
       </c>
       <c r="BT17" t="n">
-        <v>5.550177206714579e-09</v>
+        <v>4.535100073255194e-11</v>
       </c>
       <c r="BU17" t="n">
-        <v>6.810238595278406e-09</v>
+        <v>5.913131095880431e-11</v>
       </c>
       <c r="BV17" t="n">
-        <v>9.645906295929763e-09</v>
+        <v>1.253500081510595e-10</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.548500216941306e-09</v>
+        <v>1.451385955864026e-10</v>
       </c>
       <c r="BX17" t="n">
-        <v>2.144331601172667e-09</v>
+        <v>5.371987576996418e-11</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.90798310484297e-09</v>
+        <v>1.011928943417395e-10</v>
       </c>
       <c r="BZ17" t="n">
-        <v>8.336642487449808e-09</v>
+        <v>1.141516742242388e-10</v>
       </c>
       <c r="CA17" t="n">
-        <v>9.529723676848789e-09</v>
+        <v>1.402702398678457e-10</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.002003978735956e-09</v>
+        <v>8.633368325794422e-11</v>
       </c>
       <c r="CC17" t="n">
-        <v>6.625521020708902e-09</v>
+        <v>3.55693877129859e-11</v>
       </c>
       <c r="CD17" t="n">
-        <v>7.709610727602012e-10</v>
+        <v>3.709390433703774e-12</v>
       </c>
       <c r="CE17" t="n">
-        <v>7.856387540527976e-09</v>
+        <v>5.440873446227457e-11</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.681534549964226e-09</v>
+        <v>1.807063700065559e-11</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.619042760443335e-09</v>
+        <v>1.083883954811071e-10</v>
       </c>
       <c r="CH17" t="n">
-        <v>2.273170984778972e-09</v>
+        <v>9.410757589867202e-11</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.907675351020544e-09</v>
+        <v>9.454801525032863e-11</v>
       </c>
       <c r="CJ17" t="n">
-        <v>9.084407670556516e-10</v>
+        <v>1.838640871498765e-11</v>
       </c>
       <c r="CK17" t="n">
-        <v>2.558347755865498e-09</v>
+        <v>1.450877785968974e-11</v>
       </c>
       <c r="CL17" t="n">
-        <v>3.877305143618059e-09</v>
+        <v>4.578808512900601e-11</v>
       </c>
       <c r="CM17" t="n">
-        <v>1.095717916399508e-08</v>
+        <v>1.701729035463728e-10</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.04612238263735e-09</v>
+        <v>2.660974218748891e-10</v>
       </c>
       <c r="CO17" t="n">
-        <v>3.187642816371294e-09</v>
+        <v>1.709253988346759e-10</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.486161143622212e-08</v>
+        <v>4.367071287925128e-11</v>
       </c>
       <c r="CQ17" t="n">
-        <v>1.016779549445346e-08</v>
+        <v>7.979959054660313e-11</v>
       </c>
       <c r="CR17" t="n">
-        <v>7.259429501971226e-09</v>
+        <v>2.049178535190599e-11</v>
       </c>
       <c r="CS17" t="n">
-        <v>1.999710264044552e-08</v>
+        <v>1.692325724000909e-10</v>
       </c>
       <c r="CT17" t="n">
-        <v>1.527692461422703e-08</v>
+        <v>3.586320043019731e-12</v>
       </c>
       <c r="CU17" t="n">
-        <v>7.304757687620622e-09</v>
+        <v>1.795951061478451e-11</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.58127799743113e-09</v>
+        <v>7.458802672721809e-12</v>
       </c>
       <c r="CW17" t="n">
-        <v>4.954615828722808e-09</v>
+        <v>3.413518773198732e-11</v>
       </c>
       <c r="CX17" t="n">
-        <v>3.868027675935082e-09</v>
+        <v>4.960712830098801e-12</v>
       </c>
       <c r="CY17" t="n">
-        <v>6.602198787675206e-09</v>
+        <v>1.274055166922139e-10</v>
       </c>
       <c r="CZ17" t="n">
-        <v>3.764034417486073e-09</v>
+        <v>1.216521189340014e-10</v>
       </c>
       <c r="DA17" t="n">
-        <v>2.532427600954179e-10</v>
+        <v>9.683844698349375e-11</v>
       </c>
       <c r="DB17" t="n">
-        <v>4.797413577506404e-09</v>
+        <v>2.117499925402555e-11</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.767590823182786e-09</v>
+        <v>1.631575430316445e-11</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.341330240795969e-09</v>
+        <v>5.289589946610995e-11</v>
       </c>
       <c r="DE17" t="n">
-        <v>9.660473310191264e-09</v>
+        <v>1.622310619175948e-10</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.421801343326479e-08</v>
+        <v>6.473752089952711e-11</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.250510178214427e-08</v>
+        <v>5.12597464474851e-11</v>
       </c>
       <c r="DH17" t="n">
-        <v>2.35117951774555e-08</v>
+        <v>1.380960762409345e-10</v>
       </c>
       <c r="DI17" t="n">
-        <v>3.100329948324543e-08</v>
+        <v>4.714563114904813e-11</v>
       </c>
       <c r="DJ17" t="n">
-        <v>4.148882126742137e-09</v>
+        <v>2.784616703888076e-10</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.436666145579693e-09</v>
+        <v>4.479310672378389e-11</v>
       </c>
       <c r="DL17" t="n">
-        <v>2.633818318997783e-08</v>
+        <v>2.916873687031085e-11</v>
       </c>
       <c r="DM17" t="n">
-        <v>5.069050956763022e-09</v>
+        <v>1.006662669889025e-10</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.006035255102233e-08</v>
+        <v>1.046033815121916e-10</v>
       </c>
       <c r="DO17" t="n">
-        <v>3.569915696388648e-09</v>
+        <v>1.575890112848199e-10</v>
       </c>
       <c r="DP17" t="n">
-        <v>9.359425234833907e-09</v>
+        <v>1.7790106193738e-11</v>
       </c>
       <c r="DQ17" t="n">
-        <v>2.692886136301809e-09</v>
+        <v>3.082515145913511e-11</v>
       </c>
       <c r="DR17" t="n">
-        <v>4.011688314875528e-09</v>
+        <v>1.24955698566076e-10</v>
       </c>
       <c r="DS17" t="n">
-        <v>4.471569781117068e-09</v>
+        <v>4.784560941883953e-11</v>
       </c>
       <c r="DT17" t="n">
-        <v>1.819466466379538e-09</v>
+        <v>6.446698209983115e-12</v>
       </c>
       <c r="DU17" t="n">
-        <v>8.657748296059253e-09</v>
+        <v>1.769892704617249e-10</v>
       </c>
       <c r="DV17" t="n">
-        <v>1.57430246616741e-08</v>
+        <v>8.408133911341764e-11</v>
       </c>
       <c r="DW17" t="n">
-        <v>2.410374566608198e-09</v>
+        <v>6.348645220644045e-11</v>
       </c>
       <c r="DX17" t="n">
-        <v>4.379568707690851e-09</v>
+        <v>5.920432200046122e-11</v>
       </c>
       <c r="DY17" t="n">
-        <v>1.950817640761215e-08</v>
+        <v>1.128464682809138e-10</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.940123948278142e-10</v>
+        <v>1.303410573916253e-10</v>
       </c>
       <c r="EA17" t="n">
-        <v>1.449900466354848e-08</v>
+        <v>5.995980795203693e-11</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.493321022394412e-08</v>
+        <v>1.557942802543621e-10</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.367195106600661e-09</v>
+        <v>3.521856417609825e-11</v>
       </c>
       <c r="ED17" t="n">
-        <v>2.425865508470793e-09</v>
+        <v>8.939589346557142e-11</v>
       </c>
       <c r="EE17" t="n">
-        <v>6.007525032991623e-10</v>
+        <v>3.386457086973493e-11</v>
       </c>
       <c r="EF17" t="n">
-        <v>4.181536894520832e-09</v>
+        <v>4.204167222687794e-11</v>
       </c>
       <c r="EG17" t="n">
-        <v>2.296398848855574e-09</v>
+        <v>2.176580270185635e-11</v>
       </c>
       <c r="EH17" t="n">
-        <v>3.107123447421145e-09</v>
+        <v>3.195367581643183e-11</v>
       </c>
       <c r="EI17" t="n">
-        <v>5.140713632556526e-09</v>
+        <v>1.099377186508654e-10</v>
       </c>
       <c r="EJ17" t="n">
-        <v>7.314541861092039e-09</v>
+        <v>4.243692203198535e-11</v>
       </c>
       <c r="EK17" t="n">
-        <v>2.008015975718536e-09</v>
+        <v>1.150515377412731e-10</v>
       </c>
       <c r="EL17" t="n">
-        <v>6.49997389245982e-09</v>
+        <v>5.719958187655472e-11</v>
       </c>
       <c r="EM17" t="n">
-        <v>1.829704832090329e-09</v>
+        <v>5.521246220635545e-12</v>
       </c>
       <c r="EN17" t="n">
-        <v>6.058097579142441e-09</v>
+        <v>4.90640167383205e-11</v>
       </c>
       <c r="EO17" t="n">
-        <v>3.484829091959796e-09</v>
+        <v>5.8484328491204e-11</v>
       </c>
       <c r="EP17" t="n">
-        <v>3.375894452872785e-09</v>
+        <v>4.856436086608795e-11</v>
       </c>
       <c r="EQ17" t="n">
-        <v>5.516198609001322e-09</v>
+        <v>7.557951486880654e-11</v>
       </c>
       <c r="ER17" t="n">
-        <v>1.319616971251492e-09</v>
+        <v>1.165952057124997e-10</v>
       </c>
       <c r="ES17" t="n">
-        <v>4.751003146452604e-09</v>
+        <v>1.680168157380812e-12</v>
       </c>
       <c r="ET17" t="n">
-        <v>3.954386595950155e-09</v>
+        <v>1.430498774990241e-11</v>
       </c>
       <c r="EU17" t="n">
-        <v>2.853834057958693e-09</v>
+        <v>2.408130292397281e-11</v>
       </c>
       <c r="EV17" t="n">
-        <v>2.231507245653575e-08</v>
+        <v>7.117309519522053e-11</v>
       </c>
       <c r="EW17" t="n">
-        <v>1.366946733583063e-08</v>
+        <v>1.350172473824074e-10</v>
       </c>
       <c r="EX17" t="n">
-        <v>4.164191214073298e-10</v>
+        <v>2.076653952964858e-12</v>
       </c>
       <c r="EY17" t="n">
-        <v>4.654975960249885e-09</v>
+        <v>7.967156101518214e-11</v>
       </c>
       <c r="EZ17" t="n">
-        <v>2.1761450419433e-09</v>
+        <v>7.140709898378894e-12</v>
       </c>
       <c r="FA17" t="n">
-        <v>5.076011611038211e-09</v>
+        <v>1.141969990792191e-10</v>
       </c>
       <c r="FB17" t="n">
-        <v>2.817929889431525e-09</v>
+        <v>8.522039324221353e-11</v>
       </c>
       <c r="FC17" t="n">
-        <v>4.398367225988409e-10</v>
+        <v>1.013534811633576e-10</v>
       </c>
       <c r="FD17" t="n">
-        <v>2.119876496564643e-09</v>
+        <v>3.00748185036448e-12</v>
       </c>
       <c r="FE17" t="n">
-        <v>2.642281282660974e-09</v>
+        <v>3.866811731922937e-11</v>
       </c>
       <c r="FF17" t="n">
-        <v>3.103341361665457e-09</v>
+        <v>2.887701536224974e-11</v>
       </c>
       <c r="FG17" t="n">
-        <v>5.874666975103082e-09</v>
+        <v>6.759667825484428e-11</v>
       </c>
       <c r="FH17" t="n">
-        <v>1.039988184459162e-08</v>
+        <v>3.602244197375981e-11</v>
       </c>
       <c r="FI17" t="n">
-        <v>2.701771251167884e-08</v>
+        <v>1.077265568416585e-10</v>
       </c>
       <c r="FJ17" t="n">
-        <v>1.018449058420856e-08</v>
+        <v>2.005315358211135e-11</v>
       </c>
       <c r="FK17" t="n">
-        <v>1.444605590705805e-08</v>
+        <v>5.250060108874521e-11</v>
       </c>
       <c r="FL17" t="n">
-        <v>8.086523450856475e-09</v>
+        <v>3.236335158196546e-11</v>
       </c>
       <c r="FM17" t="n">
-        <v>3.030462547570778e-10</v>
+        <v>9.519171562111239e-11</v>
       </c>
       <c r="FN17" t="n">
-        <v>7.058729600828428e-09</v>
+        <v>9.538440176592999e-11</v>
       </c>
       <c r="FO17" t="n">
-        <v>9.933658340344209e-10</v>
+        <v>6.674385349958456e-11</v>
       </c>
       <c r="FP17" t="n">
-        <v>2.187473757686575e-09</v>
+        <v>1.25001120565571e-10</v>
       </c>
       <c r="FQ17" t="n">
-        <v>1.364542479009856e-09</v>
+        <v>1.080930830954507e-11</v>
       </c>
       <c r="FR17" t="n">
-        <v>1.231353019548465e-09</v>
+        <v>2.239807228576751e-10</v>
       </c>
       <c r="FS17" t="n">
-        <v>2.986279667993585e-09</v>
+        <v>9.305649306678987e-11</v>
       </c>
       <c r="FT17" t="n">
-        <v>1.249522263435665e-08</v>
+        <v>1.856503839547941e-10</v>
       </c>
       <c r="FU17" t="n">
-        <v>4.856917090734214e-09</v>
+        <v>7.675535901308095e-11</v>
       </c>
       <c r="FV17" t="n">
-        <v>1.679213212923969e-08</v>
+        <v>2.878586813359618e-10</v>
       </c>
       <c r="FW17" t="n">
-        <v>2.567366319539133e-09</v>
+        <v>1.721618680949888e-10</v>
       </c>
       <c r="FX17" t="n">
-        <v>5.423366200574264e-10</v>
+        <v>1.015337397491933e-10</v>
       </c>
       <c r="FY17" t="n">
-        <v>7.948231406373907e-09</v>
+        <v>2.311392049980654e-11</v>
       </c>
       <c r="FZ17" t="n">
-        <v>1.285581507914912e-08</v>
+        <v>1.323338244541006e-10</v>
       </c>
       <c r="GA17" t="n">
-        <v>2.450952552024432e-09</v>
+        <v>1.46371706422066e-10</v>
       </c>
       <c r="GB17" t="n">
-        <v>2.087377382054001e-09</v>
+        <v>5.947213554957642e-11</v>
       </c>
       <c r="GC17" t="n">
-        <v>6.383314765656678e-09</v>
+        <v>9.248158489016944e-11</v>
       </c>
       <c r="GD17" t="n">
-        <v>1.463381771316108e-08</v>
+        <v>2.562895728974723e-10</v>
       </c>
       <c r="GE17" t="n">
-        <v>3.953358174157984e-08</v>
+        <v>1.002678981509852e-10</v>
       </c>
       <c r="GF17" t="n">
-        <v>4.330169556254759e-09</v>
+        <v>2.813105651200409e-12</v>
       </c>
       <c r="GG17" t="n">
-        <v>2.032256674056043e-08</v>
+        <v>5.185382678796202e-11</v>
       </c>
     </row>
   </sheetData>
